--- a/data/CM-AM PERSPECTIVE CERTITUDE.xlsx
+++ b/data/CM-AM PERSPECTIVE CERTITUDE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t>Historique Cours</t>
   </si>
@@ -20,37 +20,55 @@
     <t>Date d'export</t>
   </si>
   <si>
+    <t>21/04/2026</t>
+  </si>
+  <si>
+    <t>Valeur :</t>
+  </si>
+  <si>
+    <t>Libellé valeur :</t>
+  </si>
+  <si>
+    <t>Code Isin :</t>
+  </si>
+  <si>
+    <t>P. CERTITUDE</t>
+  </si>
+  <si>
+    <t>000010001816</t>
+  </si>
+  <si>
+    <t>Se rendre en bas du document</t>
+  </si>
+  <si>
+    <t>Date de cotation</t>
+  </si>
+  <si>
+    <t>Dernier cours en EUR</t>
+  </si>
+  <si>
+    <t>Evolution en %</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>30/01/2026</t>
+  </si>
+  <si>
+    <t>31/12/2025</t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
     <t>31/10/2025</t>
-  </si>
-  <si>
-    <t>Valeur :</t>
-  </si>
-  <si>
-    <t>Libellé valeur :</t>
-  </si>
-  <si>
-    <t>Code Isin :</t>
-  </si>
-  <si>
-    <t>P. CERTITUDE</t>
-  </si>
-  <si>
-    <t>000010001816</t>
-  </si>
-  <si>
-    <t>Se rendre en bas du document</t>
-  </si>
-  <si>
-    <t>Date de cotation</t>
-  </si>
-  <si>
-    <t>Dernier cours en EUR</t>
-  </si>
-  <si>
-    <t>Evolution en %</t>
-  </si>
-  <si>
-    <t>Volume</t>
   </si>
   <si>
     <t>26/09/2025</t>
@@ -814,8 +832,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D174" headerRowCount="1">
-  <autoFilter ref="A7:D174"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D180" headerRowCount="1">
+  <autoFilter ref="A7:D180"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Date de cotation"/>
     <tableColumn id="2" name="Dernier cours en EUR"/>
@@ -828,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F175"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1" style="1"/>
@@ -942,13 +960,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="14">
-        <v>131.396</v>
+        <v>132.1515</v>
       </c>
       <c r="C8" s="15">
-        <v>0.69</v>
+        <v>-2.75</v>
       </c>
       <c r="D8" s="16">
-        <v>2764238</v>
+        <v>2896591</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -958,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B9" s="14">
-        <v>130.5011</v>
+        <v>135.8818</v>
       </c>
       <c r="C9" s="15">
-        <v>0.03</v>
+        <v>1.03</v>
       </c>
       <c r="D9" s="16">
-        <v>2763444</v>
+        <v>2856479</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -974,13 +992,13 @@
         <v>15</v>
       </c>
       <c r="B10" s="14">
-        <v>130.4589</v>
+        <v>134.4993</v>
       </c>
       <c r="C10" s="15">
-        <v>0.46</v>
+        <v>0.75</v>
       </c>
       <c r="D10" s="16">
-        <v>2760713</v>
+        <v>2849542</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
@@ -990,13 +1008,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="14">
-        <v>129.8615</v>
+        <v>133.4951</v>
       </c>
       <c r="C11" s="15">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="D11" s="16">
-        <v>2757384</v>
+        <v>2825493</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -1006,13 +1024,13 @@
         <v>17</v>
       </c>
       <c r="B12" s="14">
-        <v>129.4431</v>
+        <v>132.932</v>
       </c>
       <c r="C12" s="15">
-        <v>1.17</v>
+        <v>-0.1</v>
       </c>
       <c r="D12" s="16">
-        <v>2699976</v>
+        <v>2763616</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -1022,13 +1040,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="14">
-        <v>127.9409</v>
+        <v>133.065</v>
       </c>
       <c r="C13" s="15">
-        <v>-1.26</v>
+        <v>1.27</v>
       </c>
       <c r="D13" s="16">
-        <v>2648361</v>
+        <v>2762277</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1038,13 +1056,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="14">
-        <v>129.5692</v>
+        <v>131.396</v>
       </c>
       <c r="C14" s="15">
-        <v>-0.63</v>
+        <v>0.69</v>
       </c>
       <c r="D14" s="16">
-        <v>2617004</v>
+        <v>2764238</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
@@ -1054,13 +1072,13 @@
         <v>20</v>
       </c>
       <c r="B15" s="14">
-        <v>130.3918</v>
+        <v>130.5011</v>
       </c>
       <c r="C15" s="15">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
       <c r="D15" s="16">
-        <v>2598813</v>
+        <v>2763444</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
@@ -1070,13 +1088,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="14">
-        <v>130.172</v>
+        <v>130.4589</v>
       </c>
       <c r="C16" s="15">
-        <v>1.82</v>
+        <v>0.46</v>
       </c>
       <c r="D16" s="16">
-        <v>2595406</v>
+        <v>2760713</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
@@ -1086,13 +1104,13 @@
         <v>22</v>
       </c>
       <c r="B17" s="14">
-        <v>127.852</v>
+        <v>129.8615</v>
       </c>
       <c r="C17" s="15">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="D17" s="16">
-        <v>2584035</v>
+        <v>2757384</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
@@ -1102,13 +1120,13 @@
         <v>23</v>
       </c>
       <c r="B18" s="14">
-        <v>127.4934</v>
+        <v>129.4431</v>
       </c>
       <c r="C18" s="15">
-        <v>0.06</v>
+        <v>1.17</v>
       </c>
       <c r="D18" s="16">
-        <v>2532798</v>
+        <v>2699976</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
@@ -1118,13 +1136,13 @@
         <v>24</v>
       </c>
       <c r="B19" s="14">
-        <v>127.421</v>
+        <v>127.9409</v>
       </c>
       <c r="C19" s="15">
-        <v>-0.34</v>
+        <v>-1.26</v>
       </c>
       <c r="D19" s="16">
-        <v>2537800</v>
+        <v>2648361</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
@@ -1134,13 +1152,13 @@
         <v>25</v>
       </c>
       <c r="B20" s="14">
-        <v>127.861</v>
+        <v>129.5692</v>
       </c>
       <c r="C20" s="15">
-        <v>0.56</v>
+        <v>-0.63</v>
       </c>
       <c r="D20" s="16">
-        <v>2536370</v>
+        <v>2617004</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
@@ -1150,13 +1168,13 @@
         <v>26</v>
       </c>
       <c r="B21" s="14">
-        <v>127.1491</v>
+        <v>130.3918</v>
       </c>
       <c r="C21" s="15">
-        <v>0.61</v>
+        <v>0.17</v>
       </c>
       <c r="D21" s="16">
-        <v>2536400</v>
+        <v>2598813</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -1166,13 +1184,13 @@
         <v>27</v>
       </c>
       <c r="B22" s="14">
-        <v>126.3847</v>
+        <v>130.172</v>
       </c>
       <c r="C22" s="15">
-        <v>0.11</v>
+        <v>1.82</v>
       </c>
       <c r="D22" s="16">
-        <v>2544098</v>
+        <v>2595406</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
@@ -1182,13 +1200,13 @@
         <v>28</v>
       </c>
       <c r="B23" s="14">
-        <v>126.2419</v>
+        <v>127.852</v>
       </c>
       <c r="C23" s="15">
-        <v>-0.24</v>
+        <v>0.28</v>
       </c>
       <c r="D23" s="16">
-        <v>2535510</v>
+        <v>2584035</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
@@ -1198,13 +1216,13 @@
         <v>29</v>
       </c>
       <c r="B24" s="14">
-        <v>126.5397</v>
+        <v>127.4934</v>
       </c>
       <c r="C24" s="15">
-        <v>0.96</v>
+        <v>0.06</v>
       </c>
       <c r="D24" s="16">
-        <v>2458959</v>
+        <v>2532798</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -1214,13 +1232,13 @@
         <v>30</v>
       </c>
       <c r="B25" s="14">
-        <v>125.3313</v>
+        <v>127.421</v>
       </c>
       <c r="C25" s="15">
-        <v>-0.63</v>
+        <v>-0.34</v>
       </c>
       <c r="D25" s="16">
-        <v>2394997</v>
+        <v>2537800</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -1230,13 +1248,13 @@
         <v>31</v>
       </c>
       <c r="B26" s="14">
-        <v>126.1289</v>
+        <v>127.861</v>
       </c>
       <c r="C26" s="15">
-        <v>1.56</v>
+        <v>0.56</v>
       </c>
       <c r="D26" s="16">
-        <v>2343349</v>
+        <v>2536370</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
@@ -1246,13 +1264,13 @@
         <v>32</v>
       </c>
       <c r="B27" s="14">
-        <v>124.1917</v>
+        <v>127.1491</v>
       </c>
       <c r="C27" s="15">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="D27" s="16">
-        <v>2315769</v>
+        <v>2536400</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
@@ -1262,13 +1280,13 @@
         <v>33</v>
       </c>
       <c r="B28" s="14">
-        <v>122.3378</v>
+        <v>126.3847</v>
       </c>
       <c r="C28" s="15">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="D28" s="16">
-        <v>2317617</v>
+        <v>2544098</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
@@ -1278,13 +1296,13 @@
         <v>34</v>
       </c>
       <c r="B29" s="14">
-        <v>121.1861</v>
+        <v>126.2419</v>
       </c>
       <c r="C29" s="15">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
       <c r="D29" s="16">
-        <v>2296591</v>
+        <v>2535510</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
@@ -1294,13 +1312,13 @@
         <v>35</v>
       </c>
       <c r="B30" s="14">
-        <v>119.8562</v>
+        <v>126.5397</v>
       </c>
       <c r="C30" s="15">
-        <v>1.63</v>
+        <v>0.96</v>
       </c>
       <c r="D30" s="16">
-        <v>2254686</v>
+        <v>2458959</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
@@ -1310,13 +1328,13 @@
         <v>36</v>
       </c>
       <c r="B31" s="14">
-        <v>117.9363</v>
+        <v>125.3313</v>
       </c>
       <c r="C31" s="15">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="D31" s="16">
-        <v>2260879</v>
+        <v>2394997</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
@@ -1326,13 +1344,13 @@
         <v>37</v>
       </c>
       <c r="B32" s="14">
-        <v>118.6328</v>
+        <v>126.1289</v>
       </c>
       <c r="C32" s="15">
-        <v>-0.05</v>
+        <v>1.56</v>
       </c>
       <c r="D32" s="16">
-        <v>2263807</v>
+        <v>2343349</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
@@ -1342,13 +1360,13 @@
         <v>38</v>
       </c>
       <c r="B33" s="14">
-        <v>118.6874</v>
+        <v>124.1917</v>
       </c>
       <c r="C33" s="15">
-        <v>-0.46</v>
+        <v>1.52</v>
       </c>
       <c r="D33" s="16">
-        <v>2281551</v>
+        <v>2315769</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
@@ -1358,13 +1376,13 @@
         <v>39</v>
       </c>
       <c r="B34" s="14">
-        <v>119.2347</v>
+        <v>122.3378</v>
       </c>
       <c r="C34" s="15">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="D34" s="16">
-        <v>2279706</v>
+        <v>2317617</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
@@ -1374,13 +1392,13 @@
         <v>40</v>
       </c>
       <c r="B35" s="14">
-        <v>118.6386</v>
+        <v>121.1861</v>
       </c>
       <c r="C35" s="15">
-        <v>0.61</v>
+        <v>1.11</v>
       </c>
       <c r="D35" s="16">
-        <v>2279152</v>
+        <v>2296591</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
@@ -1390,13 +1408,13 @@
         <v>41</v>
       </c>
       <c r="B36" s="14">
-        <v>117.9168</v>
+        <v>119.8562</v>
       </c>
       <c r="C36" s="15">
-        <v>0.34</v>
+        <v>1.63</v>
       </c>
       <c r="D36" s="16">
-        <v>2202674</v>
+        <v>2254686</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
@@ -1406,13 +1424,13 @@
         <v>42</v>
       </c>
       <c r="B37" s="14">
-        <v>117.5128</v>
+        <v>117.9363</v>
       </c>
       <c r="C37" s="15">
-        <v>0.47</v>
+        <v>-0.59</v>
       </c>
       <c r="D37" s="16">
-        <v>2185588</v>
+        <v>2260879</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
@@ -1422,13 +1440,13 @@
         <v>43</v>
       </c>
       <c r="B38" s="14">
-        <v>116.9648</v>
+        <v>118.6328</v>
       </c>
       <c r="C38" s="15">
-        <v>0.33</v>
+        <v>-0.05</v>
       </c>
       <c r="D38" s="16">
-        <v>2164859</v>
+        <v>2263807</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
@@ -1438,13 +1456,13 @@
         <v>44</v>
       </c>
       <c r="B39" s="14">
-        <v>116.5833</v>
+        <v>118.6874</v>
       </c>
       <c r="C39" s="15">
-        <v>0.13</v>
+        <v>-0.46</v>
       </c>
       <c r="D39" s="16">
-        <v>2160881</v>
+        <v>2281551</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
@@ -1454,13 +1472,13 @@
         <v>45</v>
       </c>
       <c r="B40" s="14">
-        <v>116.4283</v>
+        <v>119.2347</v>
       </c>
       <c r="C40" s="15">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D40" s="16">
-        <v>2169510</v>
+        <v>2279706</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
@@ -1470,13 +1488,13 @@
         <v>46</v>
       </c>
       <c r="B41" s="14">
-        <v>115.5636</v>
+        <v>118.6386</v>
       </c>
       <c r="C41" s="15">
-        <v>-0.25</v>
+        <v>0.61</v>
       </c>
       <c r="D41" s="16">
-        <v>2163030</v>
+        <v>2279152</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
@@ -1486,13 +1504,13 @@
         <v>47</v>
       </c>
       <c r="B42" s="14">
-        <v>115.8578</v>
+        <v>117.9168</v>
       </c>
       <c r="C42" s="15">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="D42" s="16">
-        <v>2131120</v>
+        <v>2202674</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
@@ -1502,13 +1520,13 @@
         <v>48</v>
       </c>
       <c r="B43" s="14">
-        <v>115.3335</v>
+        <v>117.5128</v>
       </c>
       <c r="C43" s="15">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="D43" s="16">
-        <v>2141121</v>
+        <v>2185588</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
@@ -1518,13 +1536,13 @@
         <v>49</v>
       </c>
       <c r="B44" s="14">
-        <v>114.8751</v>
+        <v>116.9648</v>
       </c>
       <c r="C44" s="15">
-        <v>-0.72</v>
+        <v>0.33</v>
       </c>
       <c r="D44" s="16">
-        <v>2165972</v>
+        <v>2164859</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="12"/>
@@ -1534,13 +1552,13 @@
         <v>50</v>
       </c>
       <c r="B45" s="14">
-        <v>115.7123</v>
+        <v>116.5833</v>
       </c>
       <c r="C45" s="15">
-        <v>-0.25</v>
+        <v>0.13</v>
       </c>
       <c r="D45" s="16">
-        <v>2167476</v>
+        <v>2160881</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>
@@ -1550,13 +1568,13 @@
         <v>51</v>
       </c>
       <c r="B46" s="14">
-        <v>116.0035</v>
+        <v>116.4283</v>
       </c>
       <c r="C46" s="15">
-        <v>0.34</v>
+        <v>0.75</v>
       </c>
       <c r="D46" s="16">
-        <v>2169524</v>
+        <v>2169510</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
@@ -1566,13 +1584,13 @@
         <v>52</v>
       </c>
       <c r="B47" s="14">
-        <v>115.6116</v>
+        <v>115.5636</v>
       </c>
       <c r="C47" s="15">
-        <v>-0.76</v>
+        <v>-0.25</v>
       </c>
       <c r="D47" s="16">
-        <v>2160109</v>
+        <v>2163030</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="12"/>
@@ -1582,13 +1600,13 @@
         <v>53</v>
       </c>
       <c r="B48" s="14">
-        <v>116.4985</v>
+        <v>115.8578</v>
       </c>
       <c r="C48" s="15">
-        <v>-0.16</v>
+        <v>0.46</v>
       </c>
       <c r="D48" s="16">
-        <v>2089914</v>
+        <v>2131120</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
@@ -1598,13 +1616,13 @@
         <v>54</v>
       </c>
       <c r="B49" s="14">
-        <v>116.6895</v>
+        <v>115.3335</v>
       </c>
       <c r="C49" s="15">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="D49" s="16">
-        <v>2054650</v>
+        <v>2141121</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="12"/>
@@ -1614,13 +1632,13 @@
         <v>55</v>
       </c>
       <c r="B50" s="14">
-        <v>117.1621</v>
+        <v>114.8751</v>
       </c>
       <c r="C50" s="15">
-        <v>-0.33</v>
+        <v>-0.72</v>
       </c>
       <c r="D50" s="16">
-        <v>2020854</v>
+        <v>2165972</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12"/>
@@ -1630,13 +1648,13 @@
         <v>56</v>
       </c>
       <c r="B51" s="14">
-        <v>117.5474</v>
+        <v>115.7123</v>
       </c>
       <c r="C51" s="15">
-        <v>-0.46</v>
+        <v>-0.25</v>
       </c>
       <c r="D51" s="16">
-        <v>2006960</v>
+        <v>2167476</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12"/>
@@ -1646,13 +1664,13 @@
         <v>57</v>
       </c>
       <c r="B52" s="14">
-        <v>118.0891</v>
+        <v>116.0035</v>
       </c>
       <c r="C52" s="15">
-        <v>-1.37</v>
+        <v>0.34</v>
       </c>
       <c r="D52" s="16">
-        <v>2000292</v>
+        <v>2169524</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="12"/>
@@ -1662,13 +1680,13 @@
         <v>58</v>
       </c>
       <c r="B53" s="14">
-        <v>119.7273</v>
+        <v>115.6116</v>
       </c>
       <c r="C53" s="15">
-        <v>0.67</v>
+        <v>-0.76</v>
       </c>
       <c r="D53" s="16">
-        <v>1971192</v>
+        <v>2160109</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
@@ -1678,13 +1696,13 @@
         <v>59</v>
       </c>
       <c r="B54" s="14">
-        <v>118.9325</v>
+        <v>116.4985</v>
       </c>
       <c r="C54" s="15">
-        <v>-0.5</v>
+        <v>-0.16</v>
       </c>
       <c r="D54" s="16">
-        <v>1893731</v>
+        <v>2089914</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
@@ -1694,13 +1712,13 @@
         <v>60</v>
       </c>
       <c r="B55" s="14">
-        <v>119.5293</v>
+        <v>116.6895</v>
       </c>
       <c r="C55" s="15">
-        <v>0.08</v>
+        <v>-0.4</v>
       </c>
       <c r="D55" s="16">
-        <v>1888886</v>
+        <v>2054650</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="12"/>
@@ -1710,13 +1728,13 @@
         <v>61</v>
       </c>
       <c r="B56" s="14">
-        <v>119.4377</v>
+        <v>117.1621</v>
       </c>
       <c r="C56" s="15">
-        <v>-0.04</v>
+        <v>-0.33</v>
       </c>
       <c r="D56" s="16">
-        <v>1875764</v>
+        <v>2020854</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12"/>
@@ -1726,13 +1744,13 @@
         <v>62</v>
       </c>
       <c r="B57" s="14">
-        <v>119.4795</v>
+        <v>117.5474</v>
       </c>
       <c r="C57" s="15">
-        <v>0.45</v>
+        <v>-0.46</v>
       </c>
       <c r="D57" s="16">
-        <v>1882089</v>
+        <v>2006960</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12"/>
@@ -1742,13 +1760,13 @@
         <v>63</v>
       </c>
       <c r="B58" s="14">
-        <v>118.9417</v>
+        <v>118.0891</v>
       </c>
       <c r="C58" s="15">
-        <v>0</v>
+        <v>-1.37</v>
       </c>
       <c r="D58" s="16">
-        <v>1874070</v>
+        <v>2000292</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12"/>
@@ -1758,13 +1776,13 @@
         <v>64</v>
       </c>
       <c r="B59" s="14">
-        <v>118.9381</v>
+        <v>119.7273</v>
       </c>
       <c r="C59" s="15">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="D59" s="16">
-        <v>1854936</v>
+        <v>1971192</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="12"/>
@@ -1774,13 +1792,13 @@
         <v>65</v>
       </c>
       <c r="B60" s="14">
-        <v>118.5078</v>
+        <v>118.9325</v>
       </c>
       <c r="C60" s="15">
-        <v>0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="D60" s="16">
-        <v>1793350</v>
+        <v>1893731</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12"/>
@@ -1790,13 +1808,13 @@
         <v>66</v>
       </c>
       <c r="B61" s="14">
-        <v>118.0985</v>
+        <v>119.5293</v>
       </c>
       <c r="C61" s="15">
-        <v>0.49</v>
+        <v>0.08</v>
       </c>
       <c r="D61" s="16">
-        <v>1758312</v>
+        <v>1888886</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="12"/>
@@ -1806,13 +1824,13 @@
         <v>67</v>
       </c>
       <c r="B62" s="14">
-        <v>117.5179</v>
+        <v>119.4377</v>
       </c>
       <c r="C62" s="15">
-        <v>0.56</v>
+        <v>-0.04</v>
       </c>
       <c r="D62" s="16">
-        <v>1738365</v>
+        <v>1875764</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="12"/>
@@ -1822,13 +1840,13 @@
         <v>68</v>
       </c>
       <c r="B63" s="14">
-        <v>116.8645</v>
+        <v>119.4795</v>
       </c>
       <c r="C63" s="15">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="D63" s="16">
-        <v>1738745</v>
+        <v>1882089</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="12"/>
@@ -1838,13 +1856,13 @@
         <v>69</v>
       </c>
       <c r="B64" s="14">
-        <v>116.4929</v>
+        <v>118.9417</v>
       </c>
       <c r="C64" s="15">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="D64" s="16">
-        <v>1751626</v>
+        <v>1874070</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12"/>
@@ -1854,13 +1872,13 @@
         <v>70</v>
       </c>
       <c r="B65" s="14">
-        <v>116.7245</v>
+        <v>118.9381</v>
       </c>
       <c r="C65" s="15">
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="D65" s="16">
-        <v>1751432</v>
+        <v>1854936</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12"/>
@@ -1870,13 +1888,13 @@
         <v>71</v>
       </c>
       <c r="B66" s="14">
-        <v>116.5503</v>
+        <v>118.5078</v>
       </c>
       <c r="C66" s="15">
-        <v>1.05</v>
+        <v>0.35</v>
       </c>
       <c r="D66" s="16">
-        <v>1698369</v>
+        <v>1793350</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12"/>
@@ -1886,13 +1904,13 @@
         <v>72</v>
       </c>
       <c r="B67" s="14">
-        <v>115.3388</v>
+        <v>118.0985</v>
       </c>
       <c r="C67" s="15">
-        <v>-0.29</v>
+        <v>0.49</v>
       </c>
       <c r="D67" s="16">
-        <v>1699227</v>
+        <v>1758312</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
@@ -1902,13 +1920,13 @@
         <v>73</v>
       </c>
       <c r="B68" s="14">
-        <v>115.6787</v>
+        <v>117.5179</v>
       </c>
       <c r="C68" s="15">
-        <v>-0.39</v>
+        <v>0.56</v>
       </c>
       <c r="D68" s="16">
-        <v>1700256</v>
+        <v>1738365</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12"/>
@@ -1918,13 +1936,13 @@
         <v>74</v>
       </c>
       <c r="B69" s="14">
-        <v>116.1297</v>
+        <v>116.8645</v>
       </c>
       <c r="C69" s="15">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="D69" s="16">
-        <v>1699127</v>
+        <v>1738745</v>
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="12"/>
@@ -1934,13 +1952,13 @@
         <v>75</v>
       </c>
       <c r="B70" s="14">
-        <v>115.7146</v>
+        <v>116.4929</v>
       </c>
       <c r="C70" s="15">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="D70" s="16">
-        <v>1686740</v>
+        <v>1751626</v>
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
@@ -1950,13 +1968,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="14">
-        <v>115.733</v>
+        <v>116.7245</v>
       </c>
       <c r="C71" s="15">
-        <v>-0.01</v>
+        <v>0.15</v>
       </c>
       <c r="D71" s="16">
-        <v>1672215</v>
+        <v>1751432</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
@@ -1966,13 +1984,13 @@
         <v>77</v>
       </c>
       <c r="B72" s="14">
-        <v>115.7457</v>
+        <v>116.5503</v>
       </c>
       <c r="C72" s="15">
-        <v>0.25</v>
+        <v>1.05</v>
       </c>
       <c r="D72" s="16">
-        <v>1631411</v>
+        <v>1698369</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
@@ -1982,13 +2000,13 @@
         <v>78</v>
       </c>
       <c r="B73" s="14">
-        <v>115.4605</v>
+        <v>115.3388</v>
       </c>
       <c r="C73" s="15">
-        <v>0.12</v>
+        <v>-0.29</v>
       </c>
       <c r="D73" s="16">
-        <v>1612786</v>
+        <v>1699227</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12"/>
@@ -1998,13 +2016,13 @@
         <v>79</v>
       </c>
       <c r="B74" s="14">
-        <v>115.3239</v>
+        <v>115.6787</v>
       </c>
       <c r="C74" s="15">
-        <v>-2.9</v>
+        <v>-0.39</v>
       </c>
       <c r="D74" s="16">
-        <v>1600185</v>
+        <v>1700256</v>
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="12"/>
@@ -2014,13 +2032,13 @@
         <v>80</v>
       </c>
       <c r="B75" s="14">
-        <v>118.7719</v>
+        <v>116.1297</v>
       </c>
       <c r="C75" s="15">
-        <v>-1.63</v>
+        <v>0.36</v>
       </c>
       <c r="D75" s="16">
-        <v>1591763</v>
+        <v>1699127</v>
       </c>
       <c r="E75" s="12"/>
       <c r="F75" s="12"/>
@@ -2030,13 +2048,13 @@
         <v>81</v>
       </c>
       <c r="B76" s="14">
-        <v>120.7441</v>
+        <v>115.7146</v>
       </c>
       <c r="C76" s="15">
-        <v>-0.66</v>
+        <v>-0.02</v>
       </c>
       <c r="D76" s="16">
-        <v>1567275</v>
+        <v>1686740</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="12"/>
@@ -2046,13 +2064,13 @@
         <v>82</v>
       </c>
       <c r="B77" s="14">
-        <v>121.5505</v>
+        <v>115.733</v>
       </c>
       <c r="C77" s="15">
-        <v>0.6</v>
+        <v>-0.01</v>
       </c>
       <c r="D77" s="16">
-        <v>1521574</v>
+        <v>1672215</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="12"/>
@@ -2062,13 +2080,13 @@
         <v>83</v>
       </c>
       <c r="B78" s="14">
-        <v>120.829</v>
+        <v>115.7457</v>
       </c>
       <c r="C78" s="15">
-        <v>0.63</v>
+        <v>0.25</v>
       </c>
       <c r="D78" s="16">
-        <v>1453341</v>
+        <v>1631411</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="12"/>
@@ -2078,13 +2096,13 @@
         <v>84</v>
       </c>
       <c r="B79" s="14">
-        <v>120.0786</v>
+        <v>115.4605</v>
       </c>
       <c r="C79" s="15">
-        <v>0.31</v>
+        <v>0.12</v>
       </c>
       <c r="D79" s="16">
-        <v>1434243</v>
+        <v>1612786</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="12"/>
@@ -2094,13 +2112,13 @@
         <v>85</v>
       </c>
       <c r="B80" s="14">
-        <v>119.7137</v>
+        <v>115.3239</v>
       </c>
       <c r="C80" s="15">
-        <v>0.48</v>
+        <v>-2.9</v>
       </c>
       <c r="D80" s="16">
-        <v>1421467</v>
+        <v>1600185</v>
       </c>
       <c r="E80" s="12"/>
       <c r="F80" s="12"/>
@@ -2110,13 +2128,13 @@
         <v>86</v>
       </c>
       <c r="B81" s="14">
-        <v>119.1477</v>
+        <v>118.7719</v>
       </c>
       <c r="C81" s="15">
-        <v>-0.8</v>
+        <v>-1.63</v>
       </c>
       <c r="D81" s="16">
-        <v>1417271</v>
+        <v>1591763</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12"/>
@@ -2126,13 +2144,13 @@
         <v>87</v>
       </c>
       <c r="B82" s="14">
-        <v>120.1108</v>
+        <v>120.7441</v>
       </c>
       <c r="C82" s="15">
-        <v>0.45</v>
+        <v>-0.66</v>
       </c>
       <c r="D82" s="16">
-        <v>1413776</v>
+        <v>1567275</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="12"/>
@@ -2142,13 +2160,13 @@
         <v>88</v>
       </c>
       <c r="B83" s="14">
-        <v>119.5736</v>
+        <v>121.5505</v>
       </c>
       <c r="C83" s="15">
-        <v>1.16</v>
+        <v>0.6</v>
       </c>
       <c r="D83" s="16">
-        <v>1394330</v>
+        <v>1521574</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="12"/>
@@ -2158,13 +2176,13 @@
         <v>89</v>
       </c>
       <c r="B84" s="14">
-        <v>118.2007</v>
+        <v>120.829</v>
       </c>
       <c r="C84" s="15">
-        <v>-1.28</v>
+        <v>0.63</v>
       </c>
       <c r="D84" s="16">
-        <v>1320181</v>
+        <v>1453341</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="12"/>
@@ -2174,13 +2192,13 @@
         <v>90</v>
       </c>
       <c r="B85" s="14">
-        <v>119.7344</v>
+        <v>120.0786</v>
       </c>
       <c r="C85" s="15">
-        <v>0.94</v>
+        <v>0.31</v>
       </c>
       <c r="D85" s="16">
-        <v>1251436</v>
+        <v>1434243</v>
       </c>
       <c r="E85" s="12"/>
       <c r="F85" s="12"/>
@@ -2190,13 +2208,13 @@
         <v>91</v>
       </c>
       <c r="B86" s="14">
-        <v>118.6189</v>
+        <v>119.7137</v>
       </c>
       <c r="C86" s="15">
-        <v>0.32</v>
+        <v>0.48</v>
       </c>
       <c r="D86" s="16">
-        <v>1198178</v>
+        <v>1421467</v>
       </c>
       <c r="E86" s="12"/>
       <c r="F86" s="12"/>
@@ -2206,13 +2224,13 @@
         <v>92</v>
       </c>
       <c r="B87" s="14">
-        <v>118.2371</v>
+        <v>119.1477</v>
       </c>
       <c r="C87" s="15">
-        <v>0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="D87" s="16">
-        <v>1176051</v>
+        <v>1417271</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="12"/>
@@ -2222,13 +2240,13 @@
         <v>93</v>
       </c>
       <c r="B88" s="14">
-        <v>117.5348</v>
+        <v>120.1108</v>
       </c>
       <c r="C88" s="15">
-        <v>0.81</v>
+        <v>0.45</v>
       </c>
       <c r="D88" s="16">
-        <v>1166186</v>
+        <v>1413776</v>
       </c>
       <c r="E88" s="12"/>
       <c r="F88" s="12"/>
@@ -2238,13 +2256,13 @@
         <v>94</v>
       </c>
       <c r="B89" s="14">
-        <v>116.5876</v>
+        <v>119.5736</v>
       </c>
       <c r="C89" s="15">
-        <v>-1.38</v>
+        <v>1.16</v>
       </c>
       <c r="D89" s="16">
-        <v>1138715</v>
+        <v>1394330</v>
       </c>
       <c r="E89" s="12"/>
       <c r="F89" s="12"/>
@@ -2254,13 +2272,13 @@
         <v>95</v>
       </c>
       <c r="B90" s="14">
-        <v>118.2224</v>
+        <v>118.2007</v>
       </c>
       <c r="C90" s="15">
-        <v>0.36</v>
+        <v>-1.28</v>
       </c>
       <c r="D90" s="16">
-        <v>1077702</v>
+        <v>1320181</v>
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="12"/>
@@ -2270,13 +2288,13 @@
         <v>96</v>
       </c>
       <c r="B91" s="14">
-        <v>117.8047</v>
+        <v>119.7344</v>
       </c>
       <c r="C91" s="15">
-        <v>-2.27</v>
+        <v>0.94</v>
       </c>
       <c r="D91" s="16">
-        <v>1057991</v>
+        <v>1251436</v>
       </c>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
@@ -2286,13 +2304,13 @@
         <v>97</v>
       </c>
       <c r="B92" s="14">
-        <v>120.5372</v>
+        <v>118.6189</v>
       </c>
       <c r="C92" s="15">
-        <v>0.11</v>
+        <v>0.32</v>
       </c>
       <c r="D92" s="16">
-        <v>1037402</v>
+        <v>1198178</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="12"/>
@@ -2302,13 +2320,13 @@
         <v>98</v>
       </c>
       <c r="B93" s="14">
-        <v>120.4034</v>
+        <v>118.2371</v>
       </c>
       <c r="C93" s="15">
-        <v>-0.29</v>
+        <v>0.6</v>
       </c>
       <c r="D93" s="16">
-        <v>1024926</v>
+        <v>1176051</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
@@ -2318,13 +2336,13 @@
         <v>99</v>
       </c>
       <c r="B94" s="14">
-        <v>120.7502</v>
+        <v>117.5348</v>
       </c>
       <c r="C94" s="15">
-        <v>0.73</v>
+        <v>0.81</v>
       </c>
       <c r="D94" s="16">
-        <v>1004562</v>
+        <v>1166186</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12"/>
@@ -2334,13 +2352,13 @@
         <v>100</v>
       </c>
       <c r="B95" s="14">
-        <v>119.8728</v>
+        <v>116.5876</v>
       </c>
       <c r="C95" s="15">
-        <v>-0.6</v>
+        <v>-1.38</v>
       </c>
       <c r="D95" s="16">
-        <v>970004</v>
+        <v>1138715</v>
       </c>
       <c r="E95" s="12"/>
       <c r="F95" s="12"/>
@@ -2350,13 +2368,13 @@
         <v>101</v>
       </c>
       <c r="B96" s="14">
-        <v>120.6004</v>
+        <v>118.2224</v>
       </c>
       <c r="C96" s="15">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="D96" s="16">
-        <v>855569</v>
+        <v>1077702</v>
       </c>
       <c r="E96" s="12"/>
       <c r="F96" s="12"/>
@@ -2366,13 +2384,13 @@
         <v>102</v>
       </c>
       <c r="B97" s="14">
-        <v>120.1746</v>
+        <v>117.8047</v>
       </c>
       <c r="C97" s="15">
-        <v>0.88</v>
+        <v>-2.27</v>
       </c>
       <c r="D97" s="16">
-        <v>812604</v>
+        <v>1057991</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="12"/>
@@ -2382,13 +2400,13 @@
         <v>103</v>
       </c>
       <c r="B98" s="14">
-        <v>119.1224</v>
+        <v>120.5372</v>
       </c>
       <c r="C98" s="15">
-        <v>-0.61</v>
+        <v>0.11</v>
       </c>
       <c r="D98" s="16">
-        <v>779869</v>
+        <v>1037402</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="12"/>
@@ -2398,13 +2416,13 @@
         <v>104</v>
       </c>
       <c r="B99" s="14">
-        <v>119.8532</v>
+        <v>120.4034</v>
       </c>
       <c r="C99" s="15">
-        <v>-1.46</v>
+        <v>-0.29</v>
       </c>
       <c r="D99" s="16">
-        <v>707592</v>
+        <v>1024926</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
@@ -2414,13 +2432,13 @@
         <v>105</v>
       </c>
       <c r="B100" s="14">
-        <v>121.6294</v>
+        <v>120.7502</v>
       </c>
       <c r="C100" s="15">
-        <v>1.12</v>
+        <v>0.73</v>
       </c>
       <c r="D100" s="16">
-        <v>674616</v>
+        <v>1004562</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
@@ -2430,13 +2448,13 @@
         <v>106</v>
       </c>
       <c r="B101" s="14">
-        <v>120.2785</v>
+        <v>119.8728</v>
       </c>
       <c r="C101" s="15">
-        <v>-0.02</v>
+        <v>-0.6</v>
       </c>
       <c r="D101" s="16">
-        <v>638432</v>
+        <v>970004</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="12"/>
@@ -2446,13 +2464,13 @@
         <v>107</v>
       </c>
       <c r="B102" s="14">
-        <v>120.3006</v>
+        <v>120.6004</v>
       </c>
       <c r="C102" s="15">
-        <v>-0.33</v>
+        <v>0.35</v>
       </c>
       <c r="D102" s="16">
-        <v>582746</v>
+        <v>855569</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="12"/>
@@ -2462,13 +2480,13 @@
         <v>108</v>
       </c>
       <c r="B103" s="14">
-        <v>120.6971</v>
+        <v>120.1746</v>
       </c>
       <c r="C103" s="15">
-        <v>0.69</v>
+        <v>0.88</v>
       </c>
       <c r="D103" s="16">
-        <v>571304</v>
+        <v>812604</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
@@ -2478,13 +2496,13 @@
         <v>109</v>
       </c>
       <c r="B104" s="14">
-        <v>119.8736</v>
+        <v>119.1224</v>
       </c>
       <c r="C104" s="15">
-        <v>1.12</v>
+        <v>-0.61</v>
       </c>
       <c r="D104" s="16">
-        <v>547899</v>
+        <v>779869</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="12"/>
@@ -2494,13 +2512,13 @@
         <v>110</v>
       </c>
       <c r="B105" s="14">
-        <v>118.5507</v>
+        <v>119.8532</v>
       </c>
       <c r="C105" s="15">
-        <v>-0.39</v>
+        <v>-1.46</v>
       </c>
       <c r="D105" s="16">
-        <v>539122</v>
+        <v>707592</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="12"/>
@@ -2510,13 +2528,13 @@
         <v>111</v>
       </c>
       <c r="B106" s="14">
-        <v>119.0084</v>
+        <v>121.6294</v>
       </c>
       <c r="C106" s="15">
-        <v>0.19</v>
+        <v>1.12</v>
       </c>
       <c r="D106" s="16">
-        <v>532531</v>
+        <v>674616</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="12"/>
@@ -2526,13 +2544,13 @@
         <v>112</v>
       </c>
       <c r="B107" s="14">
-        <v>118.7797</v>
+        <v>120.2785</v>
       </c>
       <c r="C107" s="15">
-        <v>-0.64</v>
+        <v>-0.02</v>
       </c>
       <c r="D107" s="16">
-        <v>517833</v>
+        <v>638432</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="12"/>
@@ -2542,13 +2560,13 @@
         <v>113</v>
       </c>
       <c r="B108" s="14">
-        <v>119.5389</v>
+        <v>120.3006</v>
       </c>
       <c r="C108" s="15">
-        <v>0.48</v>
+        <v>-0.33</v>
       </c>
       <c r="D108" s="16">
-        <v>333809</v>
+        <v>582746</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="12"/>
@@ -2558,13 +2576,13 @@
         <v>114</v>
       </c>
       <c r="B109" s="14">
-        <v>118.9741</v>
+        <v>120.6971</v>
       </c>
       <c r="C109" s="15">
-        <v>0.47</v>
+        <v>0.69</v>
       </c>
       <c r="D109" s="16">
-        <v>303179</v>
+        <v>571304</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="12"/>
@@ -2574,13 +2592,13 @@
         <v>115</v>
       </c>
       <c r="B110" s="14">
-        <v>118.4181</v>
+        <v>119.8736</v>
       </c>
       <c r="C110" s="15">
-        <v>0.74</v>
+        <v>1.12</v>
       </c>
       <c r="D110" s="16">
-        <v>279520</v>
+        <v>547899</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="12"/>
@@ -2590,13 +2608,13 @@
         <v>116</v>
       </c>
       <c r="B111" s="14">
-        <v>117.5446</v>
+        <v>118.5507</v>
       </c>
       <c r="C111" s="15">
-        <v>0.11</v>
+        <v>-0.39</v>
       </c>
       <c r="D111" s="16">
-        <v>224344</v>
+        <v>539122</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="12"/>
@@ -2606,13 +2624,13 @@
         <v>117</v>
       </c>
       <c r="B112" s="14">
-        <v>117.4129</v>
+        <v>119.0084</v>
       </c>
       <c r="C112" s="15">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="D112" s="16">
-        <v>212999</v>
+        <v>532531</v>
       </c>
       <c r="E112" s="12"/>
       <c r="F112" s="12"/>
@@ -2622,13 +2640,13 @@
         <v>118</v>
       </c>
       <c r="B113" s="14">
-        <v>117.2096</v>
+        <v>118.7797</v>
       </c>
       <c r="C113" s="15">
-        <v>1.02</v>
+        <v>-0.64</v>
       </c>
       <c r="D113" s="16">
-        <v>208472</v>
+        <v>517833</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="12"/>
@@ -2638,13 +2656,13 @@
         <v>119</v>
       </c>
       <c r="B114" s="14">
-        <v>116.0317</v>
+        <v>119.5389</v>
       </c>
       <c r="C114" s="15">
-        <v>0.15</v>
+        <v>0.48</v>
       </c>
       <c r="D114" s="16">
-        <v>201455</v>
+        <v>333809</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="12"/>
@@ -2654,13 +2672,13 @@
         <v>120</v>
       </c>
       <c r="B115" s="14">
-        <v>115.8605</v>
+        <v>118.9741</v>
       </c>
       <c r="C115" s="15">
-        <v>0.17</v>
+        <v>0.47</v>
       </c>
       <c r="D115" s="16">
-        <v>177136</v>
+        <v>303179</v>
       </c>
       <c r="E115" s="12"/>
       <c r="F115" s="12"/>
@@ -2670,13 +2688,13 @@
         <v>121</v>
       </c>
       <c r="B116" s="14">
-        <v>115.6626</v>
+        <v>118.4181</v>
       </c>
       <c r="C116" s="15">
-        <v>-0.03</v>
+        <v>0.74</v>
       </c>
       <c r="D116" s="16">
-        <v>174672</v>
+        <v>279520</v>
       </c>
       <c r="E116" s="12"/>
       <c r="F116" s="12"/>
@@ -2686,13 +2704,13 @@
         <v>122</v>
       </c>
       <c r="B117" s="14">
-        <v>115.7003</v>
+        <v>117.5446</v>
       </c>
       <c r="C117" s="15">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="D117" s="16">
-        <v>174355</v>
+        <v>224344</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="12"/>
@@ -2702,13 +2720,13 @@
         <v>123</v>
       </c>
       <c r="B118" s="14">
-        <v>115.6643</v>
+        <v>117.4129</v>
       </c>
       <c r="C118" s="15">
-        <v>1.26</v>
+        <v>0.17</v>
       </c>
       <c r="D118" s="16">
-        <v>171836</v>
+        <v>212999</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="12"/>
@@ -2718,13 +2736,13 @@
         <v>124</v>
       </c>
       <c r="B119" s="14">
-        <v>114.2305</v>
+        <v>117.2096</v>
       </c>
       <c r="C119" s="15">
-        <v>-1.44</v>
+        <v>1.02</v>
       </c>
       <c r="D119" s="16">
-        <v>168640</v>
+        <v>208472</v>
       </c>
       <c r="E119" s="12"/>
       <c r="F119" s="12"/>
@@ -2734,13 +2752,13 @@
         <v>125</v>
       </c>
       <c r="B120" s="14">
-        <v>115.895</v>
+        <v>116.0317</v>
       </c>
       <c r="C120" s="15">
-        <v>0.52</v>
+        <v>0.15</v>
       </c>
       <c r="D120" s="16">
-        <v>152160</v>
+        <v>201455</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="12"/>
@@ -2750,13 +2768,13 @@
         <v>126</v>
       </c>
       <c r="B121" s="14">
-        <v>115.2905</v>
+        <v>115.8605</v>
       </c>
       <c r="C121" s="15">
-        <v>0.29</v>
+        <v>0.17</v>
       </c>
       <c r="D121" s="16">
-        <v>139488</v>
+        <v>177136</v>
       </c>
       <c r="E121" s="12"/>
       <c r="F121" s="12"/>
@@ -2766,13 +2784,13 @@
         <v>127</v>
       </c>
       <c r="B122" s="14">
-        <v>114.9604</v>
+        <v>115.6626</v>
       </c>
       <c r="C122" s="15">
-        <v>0.42</v>
+        <v>-0.03</v>
       </c>
       <c r="D122" s="16">
-        <v>131512</v>
+        <v>174672</v>
       </c>
       <c r="E122" s="12"/>
       <c r="F122" s="12"/>
@@ -2782,13 +2800,13 @@
         <v>128</v>
       </c>
       <c r="B123" s="14">
-        <v>114.4793</v>
+        <v>115.7003</v>
       </c>
       <c r="C123" s="15">
-        <v>-0.69</v>
+        <v>0.03</v>
       </c>
       <c r="D123" s="16">
-        <v>98616</v>
+        <v>174355</v>
       </c>
       <c r="E123" s="12"/>
       <c r="F123" s="12"/>
@@ -2798,13 +2816,13 @@
         <v>129</v>
       </c>
       <c r="B124" s="14">
-        <v>115.2789</v>
+        <v>115.6643</v>
       </c>
       <c r="C124" s="15">
-        <v>-1.3</v>
+        <v>1.26</v>
       </c>
       <c r="D124" s="16">
-        <v>93368</v>
+        <v>171836</v>
       </c>
       <c r="E124" s="12"/>
       <c r="F124" s="12"/>
@@ -2814,13 +2832,13 @@
         <v>130</v>
       </c>
       <c r="B125" s="14">
-        <v>116.8004</v>
+        <v>114.2305</v>
       </c>
       <c r="C125" s="15">
-        <v>-1.03</v>
+        <v>-1.44</v>
       </c>
       <c r="D125" s="16">
-        <v>91265</v>
+        <v>168640</v>
       </c>
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
@@ -2830,13 +2848,13 @@
         <v>131</v>
       </c>
       <c r="B126" s="14">
-        <v>118.0124</v>
+        <v>115.895</v>
       </c>
       <c r="C126" s="15">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="D126" s="16">
-        <v>76329</v>
+        <v>152160</v>
       </c>
       <c r="E126" s="12"/>
       <c r="F126" s="12"/>
@@ -2846,13 +2864,13 @@
         <v>132</v>
       </c>
       <c r="B127" s="14">
-        <v>117.4107</v>
+        <v>115.2905</v>
       </c>
       <c r="C127" s="15">
-        <v>1.81</v>
+        <v>0.29</v>
       </c>
       <c r="D127" s="16">
-        <v>75528</v>
+        <v>139488</v>
       </c>
       <c r="E127" s="12"/>
       <c r="F127" s="12"/>
@@ -2862,13 +2880,13 @@
         <v>133</v>
       </c>
       <c r="B128" s="14">
-        <v>115.327</v>
+        <v>114.9604</v>
       </c>
       <c r="C128" s="15">
-        <v>-1.12</v>
+        <v>0.42</v>
       </c>
       <c r="D128" s="16">
-        <v>73900</v>
+        <v>131512</v>
       </c>
       <c r="E128" s="12"/>
       <c r="F128" s="12"/>
@@ -2878,13 +2896,13 @@
         <v>134</v>
       </c>
       <c r="B129" s="14">
-        <v>116.6346</v>
+        <v>114.4793</v>
       </c>
       <c r="C129" s="15">
-        <v>-2.13</v>
+        <v>-0.69</v>
       </c>
       <c r="D129" s="16">
-        <v>73925</v>
+        <v>98616</v>
       </c>
       <c r="E129" s="12"/>
       <c r="F129" s="12"/>
@@ -2894,13 +2912,13 @@
         <v>135</v>
       </c>
       <c r="B130" s="14">
-        <v>119.1731</v>
+        <v>115.2789</v>
       </c>
       <c r="C130" s="15">
-        <v>0.04</v>
+        <v>-1.3</v>
       </c>
       <c r="D130" s="16">
-        <v>71887</v>
+        <v>93368</v>
       </c>
       <c r="E130" s="12"/>
       <c r="F130" s="12"/>
@@ -2910,13 +2928,13 @@
         <v>136</v>
       </c>
       <c r="B131" s="14">
-        <v>119.124</v>
+        <v>116.8004</v>
       </c>
       <c r="C131" s="15">
-        <v>0.18</v>
+        <v>-1.03</v>
       </c>
       <c r="D131" s="16">
-        <v>67570</v>
+        <v>91265</v>
       </c>
       <c r="E131" s="12"/>
       <c r="F131" s="12"/>
@@ -2926,13 +2944,13 @@
         <v>137</v>
       </c>
       <c r="B132" s="14">
-        <v>118.9163</v>
+        <v>118.0124</v>
       </c>
       <c r="C132" s="15">
-        <v>-0.32</v>
+        <v>0.51</v>
       </c>
       <c r="D132" s="16">
-        <v>61350</v>
+        <v>76329</v>
       </c>
       <c r="E132" s="12"/>
       <c r="F132" s="12"/>
@@ -2942,13 +2960,13 @@
         <v>138</v>
       </c>
       <c r="B133" s="14">
-        <v>119.2963</v>
+        <v>117.4107</v>
       </c>
       <c r="C133" s="15">
-        <v>0.88</v>
+        <v>1.81</v>
       </c>
       <c r="D133" s="16">
-        <v>46208</v>
+        <v>75528</v>
       </c>
       <c r="E133" s="12"/>
       <c r="F133" s="12"/>
@@ -2958,13 +2976,13 @@
         <v>139</v>
       </c>
       <c r="B134" s="14">
-        <v>118.2555</v>
+        <v>115.327</v>
       </c>
       <c r="C134" s="15">
-        <v>0.43</v>
+        <v>-1.12</v>
       </c>
       <c r="D134" s="16">
-        <v>40390</v>
+        <v>73900</v>
       </c>
       <c r="E134" s="12"/>
       <c r="F134" s="12"/>
@@ -2974,13 +2992,13 @@
         <v>140</v>
       </c>
       <c r="B135" s="14">
-        <v>117.7545</v>
+        <v>116.6346</v>
       </c>
       <c r="C135" s="15">
-        <v>2.04</v>
+        <v>-2.13</v>
       </c>
       <c r="D135" s="16">
-        <v>39114</v>
+        <v>73925</v>
       </c>
       <c r="E135" s="12"/>
       <c r="F135" s="12"/>
@@ -2990,13 +3008,13 @@
         <v>141</v>
       </c>
       <c r="B136" s="14">
-        <v>115.4039</v>
+        <v>119.1731</v>
       </c>
       <c r="C136" s="15">
-        <v>1.17</v>
+        <v>0.04</v>
       </c>
       <c r="D136" s="16">
-        <v>38151</v>
+        <v>71887</v>
       </c>
       <c r="E136" s="12"/>
       <c r="F136" s="12"/>
@@ -3006,13 +3024,13 @@
         <v>142</v>
       </c>
       <c r="B137" s="14">
-        <v>114.0721</v>
+        <v>119.124</v>
       </c>
       <c r="C137" s="15">
-        <v>-0.42</v>
+        <v>0.18</v>
       </c>
       <c r="D137" s="16">
-        <v>37695</v>
+        <v>67570</v>
       </c>
       <c r="E137" s="12"/>
       <c r="F137" s="12"/>
@@ -3022,13 +3040,13 @@
         <v>143</v>
       </c>
       <c r="B138" s="14">
-        <v>114.5545</v>
+        <v>118.9163</v>
       </c>
       <c r="C138" s="15">
-        <v>1.15</v>
+        <v>-0.32</v>
       </c>
       <c r="D138" s="16">
-        <v>35320</v>
+        <v>61350</v>
       </c>
       <c r="E138" s="12"/>
       <c r="F138" s="12"/>
@@ -3038,13 +3056,13 @@
         <v>144</v>
       </c>
       <c r="B139" s="14">
-        <v>113.2502</v>
+        <v>119.2963</v>
       </c>
       <c r="C139" s="15">
-        <v>-0.7</v>
+        <v>0.88</v>
       </c>
       <c r="D139" s="16">
-        <v>33386</v>
+        <v>46208</v>
       </c>
       <c r="E139" s="12"/>
       <c r="F139" s="12"/>
@@ -3054,13 +3072,13 @@
         <v>145</v>
       </c>
       <c r="B140" s="14">
-        <v>114.0443</v>
+        <v>118.2555</v>
       </c>
       <c r="C140" s="15">
-        <v>0.23</v>
+        <v>0.43</v>
       </c>
       <c r="D140" s="16">
-        <v>29263</v>
+        <v>40390</v>
       </c>
       <c r="E140" s="12"/>
       <c r="F140" s="12"/>
@@ -3070,13 +3088,13 @@
         <v>146</v>
       </c>
       <c r="B141" s="14">
-        <v>113.7816</v>
+        <v>117.7545</v>
       </c>
       <c r="C141" s="15">
-        <v>-0.04</v>
+        <v>2.04</v>
       </c>
       <c r="D141" s="16">
-        <v>28746</v>
+        <v>39114</v>
       </c>
       <c r="E141" s="12"/>
       <c r="F141" s="12"/>
@@ -3086,13 +3104,13 @@
         <v>147</v>
       </c>
       <c r="B142" s="14">
-        <v>113.8293</v>
+        <v>115.4039</v>
       </c>
       <c r="C142" s="15">
-        <v>-0.2</v>
+        <v>1.17</v>
       </c>
       <c r="D142" s="16">
-        <v>27943</v>
+        <v>38151</v>
       </c>
       <c r="E142" s="12"/>
       <c r="F142" s="12"/>
@@ -3102,13 +3120,13 @@
         <v>148</v>
       </c>
       <c r="B143" s="14">
-        <v>114.0562</v>
+        <v>114.0721</v>
       </c>
       <c r="C143" s="15">
-        <v>-0.09</v>
+        <v>-0.42</v>
       </c>
       <c r="D143" s="16">
-        <v>25044</v>
+        <v>37695</v>
       </c>
       <c r="E143" s="12"/>
       <c r="F143" s="12"/>
@@ -3118,13 +3136,13 @@
         <v>149</v>
       </c>
       <c r="B144" s="14">
-        <v>114.162</v>
+        <v>114.5545</v>
       </c>
       <c r="C144" s="15">
-        <v>0.85</v>
+        <v>1.15</v>
       </c>
       <c r="D144" s="16">
-        <v>23532</v>
+        <v>35320</v>
       </c>
       <c r="E144" s="12"/>
       <c r="F144" s="12"/>
@@ -3134,13 +3152,13 @@
         <v>150</v>
       </c>
       <c r="B145" s="14">
-        <v>113.2012</v>
+        <v>113.2502</v>
       </c>
       <c r="C145" s="15">
-        <v>-0.02</v>
+        <v>-0.7</v>
       </c>
       <c r="D145" s="16">
-        <v>16418</v>
+        <v>33386</v>
       </c>
       <c r="E145" s="12"/>
       <c r="F145" s="12"/>
@@ -3150,13 +3168,13 @@
         <v>151</v>
       </c>
       <c r="B146" s="14">
-        <v>113.2186</v>
+        <v>114.0443</v>
       </c>
       <c r="C146" s="15">
-        <v>0.01</v>
+        <v>0.23</v>
       </c>
       <c r="D146" s="16">
-        <v>15405</v>
+        <v>29263</v>
       </c>
       <c r="E146" s="12"/>
       <c r="F146" s="12"/>
@@ -3166,13 +3184,13 @@
         <v>152</v>
       </c>
       <c r="B147" s="14">
-        <v>113.2047</v>
+        <v>113.7816</v>
       </c>
       <c r="C147" s="15">
-        <v>1.11</v>
+        <v>-0.04</v>
       </c>
       <c r="D147" s="16">
-        <v>14808</v>
+        <v>28746</v>
       </c>
       <c r="E147" s="12"/>
       <c r="F147" s="12"/>
@@ -3182,13 +3200,13 @@
         <v>153</v>
       </c>
       <c r="B148" s="14">
-        <v>111.9598</v>
+        <v>113.8293</v>
       </c>
       <c r="C148" s="15">
-        <v>-0.72</v>
+        <v>-0.2</v>
       </c>
       <c r="D148" s="16">
-        <v>13324</v>
+        <v>27943</v>
       </c>
       <c r="E148" s="12"/>
       <c r="F148" s="12"/>
@@ -3198,13 +3216,13 @@
         <v>154</v>
       </c>
       <c r="B149" s="14">
-        <v>112.7766</v>
+        <v>114.0562</v>
       </c>
       <c r="C149" s="15">
-        <v>0.38</v>
+        <v>-0.09</v>
       </c>
       <c r="D149" s="16">
-        <v>11951</v>
+        <v>25044</v>
       </c>
       <c r="E149" s="12"/>
       <c r="F149" s="12"/>
@@ -3214,13 +3232,13 @@
         <v>155</v>
       </c>
       <c r="B150" s="14">
-        <v>112.3461</v>
+        <v>114.162</v>
       </c>
       <c r="C150" s="15">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="D150" s="16">
-        <v>7638</v>
+        <v>23532</v>
       </c>
       <c r="E150" s="12"/>
       <c r="F150" s="12"/>
@@ -3230,13 +3248,13 @@
         <v>156</v>
       </c>
       <c r="B151" s="14">
-        <v>111.3676</v>
+        <v>113.2012</v>
       </c>
       <c r="C151" s="15">
-        <v>0.33</v>
+        <v>-0.02</v>
       </c>
       <c r="D151" s="16">
-        <v>6736</v>
+        <v>16418</v>
       </c>
       <c r="E151" s="12"/>
       <c r="F151" s="12"/>
@@ -3246,13 +3264,13 @@
         <v>157</v>
       </c>
       <c r="B152" s="14">
-        <v>111.0016</v>
+        <v>113.2186</v>
       </c>
       <c r="C152" s="15">
-        <v>1.47</v>
+        <v>0.01</v>
       </c>
       <c r="D152" s="16">
-        <v>6521</v>
+        <v>15405</v>
       </c>
       <c r="E152" s="12"/>
       <c r="F152" s="12"/>
@@ -3262,13 +3280,13 @@
         <v>158</v>
       </c>
       <c r="B153" s="14">
-        <v>109.3926</v>
+        <v>113.2047</v>
       </c>
       <c r="C153" s="15">
-        <v>-0.4</v>
+        <v>1.11</v>
       </c>
       <c r="D153" s="16">
-        <v>6147</v>
+        <v>14808</v>
       </c>
       <c r="E153" s="12"/>
       <c r="F153" s="12"/>
@@ -3278,13 +3296,13 @@
         <v>159</v>
       </c>
       <c r="B154" s="14">
-        <v>109.8347</v>
+        <v>111.9598</v>
       </c>
       <c r="C154" s="15">
-        <v>1.27</v>
+        <v>-0.72</v>
       </c>
       <c r="D154" s="16">
-        <v>5381</v>
+        <v>13324</v>
       </c>
       <c r="E154" s="12"/>
       <c r="F154" s="12"/>
@@ -3294,13 +3312,13 @@
         <v>160</v>
       </c>
       <c r="B155" s="14">
-        <v>108.4628</v>
+        <v>112.7766</v>
       </c>
       <c r="C155" s="15">
-        <v>-0.98</v>
+        <v>0.38</v>
       </c>
       <c r="D155" s="16">
-        <v>4975</v>
+        <v>11951</v>
       </c>
       <c r="E155" s="12"/>
       <c r="F155" s="12"/>
@@ -3310,13 +3328,13 @@
         <v>161</v>
       </c>
       <c r="B156" s="14">
-        <v>109.5329</v>
+        <v>112.3461</v>
       </c>
       <c r="C156" s="15">
-        <v>1.31</v>
+        <v>0.88</v>
       </c>
       <c r="D156" s="16">
-        <v>4423</v>
+        <v>7638</v>
       </c>
       <c r="E156" s="12"/>
       <c r="F156" s="12"/>
@@ -3326,13 +3344,13 @@
         <v>162</v>
       </c>
       <c r="B157" s="14">
-        <v>108.1217</v>
+        <v>111.3676</v>
       </c>
       <c r="C157" s="15">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="D157" s="16">
-        <v>1540</v>
+        <v>6736</v>
       </c>
       <c r="E157" s="12"/>
       <c r="F157" s="12"/>
@@ -3342,13 +3360,13 @@
         <v>163</v>
       </c>
       <c r="B158" s="14">
-        <v>107.2595</v>
+        <v>111.0016</v>
       </c>
       <c r="C158" s="15">
-        <v>0.68</v>
+        <v>1.47</v>
       </c>
       <c r="D158" s="16">
-        <v>1203</v>
+        <v>6521</v>
       </c>
       <c r="E158" s="12"/>
       <c r="F158" s="12"/>
@@ -3358,13 +3376,13 @@
         <v>164</v>
       </c>
       <c r="B159" s="14">
-        <v>106.5371</v>
+        <v>109.3926</v>
       </c>
       <c r="C159" s="15">
-        <v>-0.05</v>
+        <v>-0.4</v>
       </c>
       <c r="D159" s="16">
-        <v>1160</v>
+        <v>6147</v>
       </c>
       <c r="E159" s="12"/>
       <c r="F159" s="12"/>
@@ -3374,13 +3392,13 @@
         <v>165</v>
       </c>
       <c r="B160" s="14">
-        <v>106.5848</v>
+        <v>109.8347</v>
       </c>
       <c r="C160" s="15">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="D160" s="16">
-        <v>1087</v>
+        <v>5381</v>
       </c>
       <c r="E160" s="12"/>
       <c r="F160" s="12"/>
@@ -3390,13 +3408,13 @@
         <v>166</v>
       </c>
       <c r="B161" s="14">
-        <v>104.885</v>
+        <v>108.4628</v>
       </c>
       <c r="C161" s="15">
-        <v>0.88</v>
+        <v>-0.98</v>
       </c>
       <c r="D161" s="16">
-        <v>1064</v>
+        <v>4975</v>
       </c>
       <c r="E161" s="12"/>
       <c r="F161" s="12"/>
@@ -3406,13 +3424,13 @@
         <v>167</v>
       </c>
       <c r="B162" s="14">
-        <v>103.9697</v>
+        <v>109.5329</v>
       </c>
       <c r="C162" s="15">
-        <v>0.95</v>
+        <v>1.31</v>
       </c>
       <c r="D162" s="16">
-        <v>1007</v>
+        <v>4423</v>
       </c>
       <c r="E162" s="12"/>
       <c r="F162" s="12"/>
@@ -3422,13 +3440,13 @@
         <v>168</v>
       </c>
       <c r="B163" s="14">
-        <v>102.9955</v>
+        <v>108.1217</v>
       </c>
       <c r="C163" s="15">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="D163" s="16">
-        <v>1011</v>
+        <v>1540</v>
       </c>
       <c r="E163" s="12"/>
       <c r="F163" s="12"/>
@@ -3438,13 +3456,13 @@
         <v>169</v>
       </c>
       <c r="B164" s="14">
-        <v>102.8921</v>
+        <v>107.2595</v>
       </c>
       <c r="C164" s="15">
-        <v>0.3</v>
+        <v>0.68</v>
       </c>
       <c r="D164" s="16">
-        <v>1000</v>
+        <v>1203</v>
       </c>
       <c r="E164" s="12"/>
       <c r="F164" s="12"/>
@@ -3454,13 +3472,13 @@
         <v>170</v>
       </c>
       <c r="B165" s="14">
-        <v>102.5829</v>
+        <v>106.5371</v>
       </c>
       <c r="C165" s="15">
-        <v>0.75</v>
+        <v>-0.05</v>
       </c>
       <c r="D165" s="16">
-        <v>987</v>
+        <v>1160</v>
       </c>
       <c r="E165" s="12"/>
       <c r="F165" s="12"/>
@@ -3470,13 +3488,13 @@
         <v>171</v>
       </c>
       <c r="B166" s="14">
-        <v>101.8247</v>
+        <v>106.5848</v>
       </c>
       <c r="C166" s="15">
-        <v>0.37</v>
+        <v>1.62</v>
       </c>
       <c r="D166" s="16">
-        <v>823</v>
+        <v>1087</v>
       </c>
       <c r="E166" s="12"/>
       <c r="F166" s="12"/>
@@ -3486,13 +3504,13 @@
         <v>172</v>
       </c>
       <c r="B167" s="14">
-        <v>101.4515</v>
+        <v>104.885</v>
       </c>
       <c r="C167" s="15">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="D167" s="16">
-        <v>782</v>
+        <v>1064</v>
       </c>
       <c r="E167" s="12"/>
       <c r="F167" s="12"/>
@@ -3502,13 +3520,13 @@
         <v>173</v>
       </c>
       <c r="B168" s="14">
-        <v>100.5858</v>
+        <v>103.9697</v>
       </c>
       <c r="C168" s="15">
-        <v>-1.46</v>
+        <v>0.95</v>
       </c>
       <c r="D168" s="16">
-        <v>686</v>
+        <v>1007</v>
       </c>
       <c r="E168" s="12"/>
       <c r="F168" s="12"/>
@@ -3518,13 +3536,13 @@
         <v>174</v>
       </c>
       <c r="B169" s="14">
-        <v>102.0741</v>
+        <v>102.9955</v>
       </c>
       <c r="C169" s="15">
-        <v>-0.69</v>
+        <v>0.1</v>
       </c>
       <c r="D169" s="16">
-        <v>142</v>
+        <v>1011</v>
       </c>
       <c r="E169" s="12"/>
       <c r="F169" s="12"/>
@@ -3534,13 +3552,13 @@
         <v>175</v>
       </c>
       <c r="B170" s="14">
-        <v>102.7852</v>
+        <v>102.8921</v>
       </c>
       <c r="C170" s="15">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="D170" s="16">
-        <v>72</v>
+        <v>1000</v>
       </c>
       <c r="E170" s="12"/>
       <c r="F170" s="12"/>
@@ -3550,13 +3568,13 @@
         <v>176</v>
       </c>
       <c r="B171" s="14">
-        <v>102.4336</v>
+        <v>102.5829</v>
       </c>
       <c r="C171" s="15">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="D171" s="16">
-        <v>54</v>
+        <v>987</v>
       </c>
       <c r="E171" s="12"/>
       <c r="F171" s="12"/>
@@ -3566,13 +3584,13 @@
         <v>177</v>
       </c>
       <c r="B172" s="14">
-        <v>101.309</v>
+        <v>101.8247</v>
       </c>
       <c r="C172" s="15">
-        <v>1.31</v>
+        <v>0.37</v>
       </c>
       <c r="D172" s="16">
-        <v>53</v>
+        <v>823</v>
       </c>
       <c r="E172" s="12"/>
       <c r="F172" s="12"/>
@@ -3582,13 +3600,13 @@
         <v>178</v>
       </c>
       <c r="B173" s="14">
-        <v>100.0034</v>
+        <v>101.4515</v>
       </c>
       <c r="C173" s="15">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="D173" s="16">
-        <v>53</v>
+        <v>782</v>
       </c>
       <c r="E173" s="12"/>
       <c r="F173" s="12"/>
@@ -3598,29 +3616,125 @@
         <v>179</v>
       </c>
       <c r="B174" s="14">
-        <v>100</v>
-      </c>
-      <c r="C174" s="17" t="s">
-        <v>180</v>
+        <v>100.5858</v>
+      </c>
+      <c r="C174" s="15">
+        <v>-1.46</v>
       </c>
       <c r="D174" s="16">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="E174" s="12"/>
       <c r="F174" s="12"/>
     </row>
-    <row r="175" ht="35" customHeight="1">
-      <c r="A175" s="18" t="s">
+    <row r="175" s="12" customFormat="1">
+      <c r="A175" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B175" s="14">
+        <v>102.0741</v>
+      </c>
+      <c r="C175" s="15">
+        <v>-0.69</v>
+      </c>
+      <c r="D175" s="16">
+        <v>142</v>
+      </c>
+      <c r="E175" s="12"/>
+      <c r="F175" s="12"/>
+    </row>
+    <row r="176" s="12" customFormat="1">
+      <c r="A176" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="B175" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C175" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="D175" s="18" t="s">
-        <v>181</v>
+      <c r="B176" s="14">
+        <v>102.7852</v>
+      </c>
+      <c r="C176" s="15">
+        <v>0.34</v>
+      </c>
+      <c r="D176" s="16">
+        <v>72</v>
+      </c>
+      <c r="E176" s="12"/>
+      <c r="F176" s="12"/>
+    </row>
+    <row r="177" s="12" customFormat="1">
+      <c r="A177" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B177" s="14">
+        <v>102.4336</v>
+      </c>
+      <c r="C177" s="15">
+        <v>1.11</v>
+      </c>
+      <c r="D177" s="16">
+        <v>54</v>
+      </c>
+      <c r="E177" s="12"/>
+      <c r="F177" s="12"/>
+    </row>
+    <row r="178" s="12" customFormat="1">
+      <c r="A178" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B178" s="14">
+        <v>101.309</v>
+      </c>
+      <c r="C178" s="15">
+        <v>1.31</v>
+      </c>
+      <c r="D178" s="16">
+        <v>53</v>
+      </c>
+      <c r="E178" s="12"/>
+      <c r="F178" s="12"/>
+    </row>
+    <row r="179" s="12" customFormat="1">
+      <c r="A179" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B179" s="14">
+        <v>100.0034</v>
+      </c>
+      <c r="C179" s="15">
+        <v>0</v>
+      </c>
+      <c r="D179" s="16">
+        <v>53</v>
+      </c>
+      <c r="E179" s="12"/>
+      <c r="F179" s="12"/>
+    </row>
+    <row r="180" s="12" customFormat="1">
+      <c r="A180" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B180" s="14">
+        <v>100</v>
+      </c>
+      <c r="C180" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D180" s="16">
+        <v>0</v>
+      </c>
+      <c r="E180" s="12"/>
+      <c r="F180" s="12"/>
+    </row>
+    <row r="181" ht="35" customHeight="1">
+      <c r="A181" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B181" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C181" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="D181" s="18" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -3636,18 +3750,18 @@
     <mergeCell ref="E4:E4"/>
     <mergeCell ref="E5:E5"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A175:D175"/>
+    <mergeCell ref="A181:D181"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A6" location="'Historique Cours'!A175" display="Se rendre en bas du document"/>
-    <hyperlink ref="B6" location="'Historique Cours'!A175" display="Se rendre en bas du document"/>
-    <hyperlink ref="C6" location="'Historique Cours'!A175" display="Se rendre en bas du document"/>
-    <hyperlink ref="D6" location="'Historique Cours'!A175" display="Se rendre en bas du document"/>
-    <hyperlink ref="E6" location="'Historique Cours'!A175" display="Se rendre en bas du document"/>
-    <hyperlink ref="A175" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="B175" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="C175" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="D175" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="A6" location="'Historique Cours'!A181" display="Se rendre en bas du document"/>
+    <hyperlink ref="B6" location="'Historique Cours'!A181" display="Se rendre en bas du document"/>
+    <hyperlink ref="C6" location="'Historique Cours'!A181" display="Se rendre en bas du document"/>
+    <hyperlink ref="D6" location="'Historique Cours'!A181" display="Se rendre en bas du document"/>
+    <hyperlink ref="E6" location="'Historique Cours'!A181" display="Se rendre en bas du document"/>
+    <hyperlink ref="A181" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="B181" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="C181" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="D181" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
   </hyperlinks>
   <headerFooter/>
   <tableParts>

--- a/data/CM-AM PERSPECTIVE CERTITUDE.xlsx
+++ b/data/CM-AM PERSPECTIVE CERTITUDE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <si>
     <t>Historique Cours</t>
   </si>
@@ -20,7 +20,7 @@
     <t>Date d'export</t>
   </si>
   <si>
-    <t>21/04/2026</t>
+    <t>21/10/2026</t>
   </si>
   <si>
     <t>Valeur :</t>
@@ -51,6 +51,24 @@
   </si>
   <si>
     <t>Volume</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>31/07/2026</t>
+  </si>
+  <si>
+    <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>29/05/2026</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
   </si>
   <si>
     <t>27/03/2026</t>
@@ -832,8 +850,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D180" headerRowCount="1">
-  <autoFilter ref="A7:D180"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D186" headerRowCount="1">
+  <autoFilter ref="A7:D186"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Date de cotation"/>
     <tableColumn id="2" name="Dernier cours en EUR"/>
@@ -846,7 +864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F181"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1" style="1"/>
@@ -960,13 +978,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="14">
-        <v>132.1515</v>
+        <v>137.644</v>
       </c>
       <c r="C8" s="15">
-        <v>-2.75</v>
+        <v>-0.36</v>
       </c>
       <c r="D8" s="16">
-        <v>2896591</v>
+        <v>2895028</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -976,13 +994,13 @@
         <v>14</v>
       </c>
       <c r="B9" s="14">
-        <v>135.8818</v>
+        <v>138.1404</v>
       </c>
       <c r="C9" s="15">
-        <v>1.03</v>
+        <v>0.61</v>
       </c>
       <c r="D9" s="16">
-        <v>2856479</v>
+        <v>2894633</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -992,13 +1010,13 @@
         <v>15</v>
       </c>
       <c r="B10" s="14">
-        <v>134.4993</v>
+        <v>137.2997</v>
       </c>
       <c r="C10" s="15">
-        <v>0.75</v>
+        <v>0.18</v>
       </c>
       <c r="D10" s="16">
-        <v>2849542</v>
+        <v>2890268</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
@@ -1008,13 +1026,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="14">
-        <v>133.4951</v>
+        <v>137.0575</v>
       </c>
       <c r="C11" s="15">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="D11" s="16">
-        <v>2825493</v>
+        <v>3146132</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -1024,13 +1042,13 @@
         <v>17</v>
       </c>
       <c r="B12" s="14">
-        <v>132.932</v>
+        <v>136.4596</v>
       </c>
       <c r="C12" s="15">
-        <v>-0.1</v>
+        <v>1.25</v>
       </c>
       <c r="D12" s="16">
-        <v>2763616</v>
+        <v>3025991</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -1040,13 +1058,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="14">
-        <v>133.065</v>
+        <v>134.7778</v>
       </c>
       <c r="C13" s="15">
-        <v>1.27</v>
+        <v>1.99</v>
       </c>
       <c r="D13" s="16">
-        <v>2762277</v>
+        <v>2945117</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1056,13 +1074,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="14">
-        <v>131.396</v>
+        <v>132.1515</v>
       </c>
       <c r="C14" s="15">
-        <v>0.69</v>
+        <v>-2.75</v>
       </c>
       <c r="D14" s="16">
-        <v>2764238</v>
+        <v>2896591</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
@@ -1072,13 +1090,13 @@
         <v>20</v>
       </c>
       <c r="B15" s="14">
-        <v>130.5011</v>
+        <v>135.8818</v>
       </c>
       <c r="C15" s="15">
-        <v>0.03</v>
+        <v>1.03</v>
       </c>
       <c r="D15" s="16">
-        <v>2763444</v>
+        <v>2856479</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
@@ -1088,13 +1106,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="14">
-        <v>130.4589</v>
+        <v>134.4993</v>
       </c>
       <c r="C16" s="15">
-        <v>0.46</v>
+        <v>0.75</v>
       </c>
       <c r="D16" s="16">
-        <v>2760713</v>
+        <v>2849542</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
@@ -1104,13 +1122,13 @@
         <v>22</v>
       </c>
       <c r="B17" s="14">
-        <v>129.8615</v>
+        <v>133.4951</v>
       </c>
       <c r="C17" s="15">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="D17" s="16">
-        <v>2757384</v>
+        <v>2825493</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
@@ -1120,13 +1138,13 @@
         <v>23</v>
       </c>
       <c r="B18" s="14">
-        <v>129.4431</v>
+        <v>132.932</v>
       </c>
       <c r="C18" s="15">
-        <v>1.17</v>
+        <v>-0.1</v>
       </c>
       <c r="D18" s="16">
-        <v>2699976</v>
+        <v>2763616</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
@@ -1136,13 +1154,13 @@
         <v>24</v>
       </c>
       <c r="B19" s="14">
-        <v>127.9409</v>
+        <v>133.065</v>
       </c>
       <c r="C19" s="15">
-        <v>-1.26</v>
+        <v>1.27</v>
       </c>
       <c r="D19" s="16">
-        <v>2648361</v>
+        <v>2762277</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
@@ -1152,13 +1170,13 @@
         <v>25</v>
       </c>
       <c r="B20" s="14">
-        <v>129.5692</v>
+        <v>131.396</v>
       </c>
       <c r="C20" s="15">
-        <v>-0.63</v>
+        <v>0.69</v>
       </c>
       <c r="D20" s="16">
-        <v>2617004</v>
+        <v>2764238</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
@@ -1168,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="B21" s="14">
-        <v>130.3918</v>
+        <v>130.5011</v>
       </c>
       <c r="C21" s="15">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
       <c r="D21" s="16">
-        <v>2598813</v>
+        <v>2763444</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -1184,13 +1202,13 @@
         <v>27</v>
       </c>
       <c r="B22" s="14">
-        <v>130.172</v>
+        <v>130.4589</v>
       </c>
       <c r="C22" s="15">
-        <v>1.82</v>
+        <v>0.46</v>
       </c>
       <c r="D22" s="16">
-        <v>2595406</v>
+        <v>2760713</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
@@ -1200,13 +1218,13 @@
         <v>28</v>
       </c>
       <c r="B23" s="14">
-        <v>127.852</v>
+        <v>129.8615</v>
       </c>
       <c r="C23" s="15">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="D23" s="16">
-        <v>2584035</v>
+        <v>2757384</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
@@ -1216,13 +1234,13 @@
         <v>29</v>
       </c>
       <c r="B24" s="14">
-        <v>127.4934</v>
+        <v>129.4431</v>
       </c>
       <c r="C24" s="15">
-        <v>0.06</v>
+        <v>1.17</v>
       </c>
       <c r="D24" s="16">
-        <v>2532798</v>
+        <v>2699976</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -1232,13 +1250,13 @@
         <v>30</v>
       </c>
       <c r="B25" s="14">
-        <v>127.421</v>
+        <v>127.9409</v>
       </c>
       <c r="C25" s="15">
-        <v>-0.34</v>
+        <v>-1.26</v>
       </c>
       <c r="D25" s="16">
-        <v>2537800</v>
+        <v>2648361</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -1248,13 +1266,13 @@
         <v>31</v>
       </c>
       <c r="B26" s="14">
-        <v>127.861</v>
+        <v>129.5692</v>
       </c>
       <c r="C26" s="15">
-        <v>0.56</v>
+        <v>-0.63</v>
       </c>
       <c r="D26" s="16">
-        <v>2536370</v>
+        <v>2617004</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
@@ -1264,13 +1282,13 @@
         <v>32</v>
       </c>
       <c r="B27" s="14">
-        <v>127.1491</v>
+        <v>130.3918</v>
       </c>
       <c r="C27" s="15">
-        <v>0.61</v>
+        <v>0.17</v>
       </c>
       <c r="D27" s="16">
-        <v>2536400</v>
+        <v>2598813</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
@@ -1280,13 +1298,13 @@
         <v>33</v>
       </c>
       <c r="B28" s="14">
-        <v>126.3847</v>
+        <v>130.172</v>
       </c>
       <c r="C28" s="15">
-        <v>0.11</v>
+        <v>1.82</v>
       </c>
       <c r="D28" s="16">
-        <v>2544098</v>
+        <v>2595406</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
@@ -1296,13 +1314,13 @@
         <v>34</v>
       </c>
       <c r="B29" s="14">
-        <v>126.2419</v>
+        <v>127.852</v>
       </c>
       <c r="C29" s="15">
-        <v>-0.24</v>
+        <v>0.28</v>
       </c>
       <c r="D29" s="16">
-        <v>2535510</v>
+        <v>2584035</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
@@ -1312,13 +1330,13 @@
         <v>35</v>
       </c>
       <c r="B30" s="14">
-        <v>126.5397</v>
+        <v>127.4934</v>
       </c>
       <c r="C30" s="15">
-        <v>0.96</v>
+        <v>0.06</v>
       </c>
       <c r="D30" s="16">
-        <v>2458959</v>
+        <v>2532798</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
@@ -1328,13 +1346,13 @@
         <v>36</v>
       </c>
       <c r="B31" s="14">
-        <v>125.3313</v>
+        <v>127.421</v>
       </c>
       <c r="C31" s="15">
-        <v>-0.63</v>
+        <v>-0.34</v>
       </c>
       <c r="D31" s="16">
-        <v>2394997</v>
+        <v>2537800</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
@@ -1344,13 +1362,13 @@
         <v>37</v>
       </c>
       <c r="B32" s="14">
-        <v>126.1289</v>
+        <v>127.861</v>
       </c>
       <c r="C32" s="15">
-        <v>1.56</v>
+        <v>0.56</v>
       </c>
       <c r="D32" s="16">
-        <v>2343349</v>
+        <v>2536370</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
@@ -1360,13 +1378,13 @@
         <v>38</v>
       </c>
       <c r="B33" s="14">
-        <v>124.1917</v>
+        <v>127.1491</v>
       </c>
       <c r="C33" s="15">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="D33" s="16">
-        <v>2315769</v>
+        <v>2536400</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
@@ -1376,13 +1394,13 @@
         <v>39</v>
       </c>
       <c r="B34" s="14">
-        <v>122.3378</v>
+        <v>126.3847</v>
       </c>
       <c r="C34" s="15">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="D34" s="16">
-        <v>2317617</v>
+        <v>2544098</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
@@ -1392,13 +1410,13 @@
         <v>40</v>
       </c>
       <c r="B35" s="14">
-        <v>121.1861</v>
+        <v>126.2419</v>
       </c>
       <c r="C35" s="15">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
       <c r="D35" s="16">
-        <v>2296591</v>
+        <v>2535510</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
@@ -1408,13 +1426,13 @@
         <v>41</v>
       </c>
       <c r="B36" s="14">
-        <v>119.8562</v>
+        <v>126.5397</v>
       </c>
       <c r="C36" s="15">
-        <v>1.63</v>
+        <v>0.96</v>
       </c>
       <c r="D36" s="16">
-        <v>2254686</v>
+        <v>2458959</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
@@ -1424,13 +1442,13 @@
         <v>42</v>
       </c>
       <c r="B37" s="14">
-        <v>117.9363</v>
+        <v>125.3313</v>
       </c>
       <c r="C37" s="15">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="D37" s="16">
-        <v>2260879</v>
+        <v>2394997</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
@@ -1440,13 +1458,13 @@
         <v>43</v>
       </c>
       <c r="B38" s="14">
-        <v>118.6328</v>
+        <v>126.1289</v>
       </c>
       <c r="C38" s="15">
-        <v>-0.05</v>
+        <v>1.56</v>
       </c>
       <c r="D38" s="16">
-        <v>2263807</v>
+        <v>2343349</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
@@ -1456,13 +1474,13 @@
         <v>44</v>
       </c>
       <c r="B39" s="14">
-        <v>118.6874</v>
+        <v>124.1917</v>
       </c>
       <c r="C39" s="15">
-        <v>-0.46</v>
+        <v>1.52</v>
       </c>
       <c r="D39" s="16">
-        <v>2281551</v>
+        <v>2315769</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
@@ -1472,13 +1490,13 @@
         <v>45</v>
       </c>
       <c r="B40" s="14">
-        <v>119.2347</v>
+        <v>122.3378</v>
       </c>
       <c r="C40" s="15">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="D40" s="16">
-        <v>2279706</v>
+        <v>2317617</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
@@ -1488,13 +1506,13 @@
         <v>46</v>
       </c>
       <c r="B41" s="14">
-        <v>118.6386</v>
+        <v>121.1861</v>
       </c>
       <c r="C41" s="15">
-        <v>0.61</v>
+        <v>1.11</v>
       </c>
       <c r="D41" s="16">
-        <v>2279152</v>
+        <v>2296591</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
@@ -1504,13 +1522,13 @@
         <v>47</v>
       </c>
       <c r="B42" s="14">
-        <v>117.9168</v>
+        <v>119.8562</v>
       </c>
       <c r="C42" s="15">
-        <v>0.34</v>
+        <v>1.63</v>
       </c>
       <c r="D42" s="16">
-        <v>2202674</v>
+        <v>2254686</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
@@ -1520,13 +1538,13 @@
         <v>48</v>
       </c>
       <c r="B43" s="14">
-        <v>117.5128</v>
+        <v>117.9363</v>
       </c>
       <c r="C43" s="15">
-        <v>0.47</v>
+        <v>-0.59</v>
       </c>
       <c r="D43" s="16">
-        <v>2185588</v>
+        <v>2260879</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
@@ -1536,13 +1554,13 @@
         <v>49</v>
       </c>
       <c r="B44" s="14">
-        <v>116.9648</v>
+        <v>118.6328</v>
       </c>
       <c r="C44" s="15">
-        <v>0.33</v>
+        <v>-0.05</v>
       </c>
       <c r="D44" s="16">
-        <v>2164859</v>
+        <v>2263807</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="12"/>
@@ -1552,13 +1570,13 @@
         <v>50</v>
       </c>
       <c r="B45" s="14">
-        <v>116.5833</v>
+        <v>118.6874</v>
       </c>
       <c r="C45" s="15">
-        <v>0.13</v>
+        <v>-0.46</v>
       </c>
       <c r="D45" s="16">
-        <v>2160881</v>
+        <v>2281551</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>
@@ -1568,13 +1586,13 @@
         <v>51</v>
       </c>
       <c r="B46" s="14">
-        <v>116.4283</v>
+        <v>119.2347</v>
       </c>
       <c r="C46" s="15">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D46" s="16">
-        <v>2169510</v>
+        <v>2279706</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
@@ -1584,13 +1602,13 @@
         <v>52</v>
       </c>
       <c r="B47" s="14">
-        <v>115.5636</v>
+        <v>118.6386</v>
       </c>
       <c r="C47" s="15">
-        <v>-0.25</v>
+        <v>0.61</v>
       </c>
       <c r="D47" s="16">
-        <v>2163030</v>
+        <v>2279152</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="12"/>
@@ -1600,13 +1618,13 @@
         <v>53</v>
       </c>
       <c r="B48" s="14">
-        <v>115.8578</v>
+        <v>117.9168</v>
       </c>
       <c r="C48" s="15">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="D48" s="16">
-        <v>2131120</v>
+        <v>2202674</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
@@ -1616,13 +1634,13 @@
         <v>54</v>
       </c>
       <c r="B49" s="14">
-        <v>115.3335</v>
+        <v>117.5128</v>
       </c>
       <c r="C49" s="15">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="D49" s="16">
-        <v>2141121</v>
+        <v>2185588</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="12"/>
@@ -1632,13 +1650,13 @@
         <v>55</v>
       </c>
       <c r="B50" s="14">
-        <v>114.8751</v>
+        <v>116.9648</v>
       </c>
       <c r="C50" s="15">
-        <v>-0.72</v>
+        <v>0.33</v>
       </c>
       <c r="D50" s="16">
-        <v>2165972</v>
+        <v>2164859</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12"/>
@@ -1648,13 +1666,13 @@
         <v>56</v>
       </c>
       <c r="B51" s="14">
-        <v>115.7123</v>
+        <v>116.5833</v>
       </c>
       <c r="C51" s="15">
-        <v>-0.25</v>
+        <v>0.13</v>
       </c>
       <c r="D51" s="16">
-        <v>2167476</v>
+        <v>2160881</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12"/>
@@ -1664,13 +1682,13 @@
         <v>57</v>
       </c>
       <c r="B52" s="14">
-        <v>116.0035</v>
+        <v>116.4283</v>
       </c>
       <c r="C52" s="15">
-        <v>0.34</v>
+        <v>0.75</v>
       </c>
       <c r="D52" s="16">
-        <v>2169524</v>
+        <v>2169510</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="12"/>
@@ -1680,13 +1698,13 @@
         <v>58</v>
       </c>
       <c r="B53" s="14">
-        <v>115.6116</v>
+        <v>115.5636</v>
       </c>
       <c r="C53" s="15">
-        <v>-0.76</v>
+        <v>-0.25</v>
       </c>
       <c r="D53" s="16">
-        <v>2160109</v>
+        <v>2163030</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
@@ -1696,13 +1714,13 @@
         <v>59</v>
       </c>
       <c r="B54" s="14">
-        <v>116.4985</v>
+        <v>115.8578</v>
       </c>
       <c r="C54" s="15">
-        <v>-0.16</v>
+        <v>0.46</v>
       </c>
       <c r="D54" s="16">
-        <v>2089914</v>
+        <v>2131120</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
@@ -1712,13 +1730,13 @@
         <v>60</v>
       </c>
       <c r="B55" s="14">
-        <v>116.6895</v>
+        <v>115.3335</v>
       </c>
       <c r="C55" s="15">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="D55" s="16">
-        <v>2054650</v>
+        <v>2141121</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="12"/>
@@ -1728,13 +1746,13 @@
         <v>61</v>
       </c>
       <c r="B56" s="14">
-        <v>117.1621</v>
+        <v>114.8751</v>
       </c>
       <c r="C56" s="15">
-        <v>-0.33</v>
+        <v>-0.72</v>
       </c>
       <c r="D56" s="16">
-        <v>2020854</v>
+        <v>2165972</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12"/>
@@ -1744,13 +1762,13 @@
         <v>62</v>
       </c>
       <c r="B57" s="14">
-        <v>117.5474</v>
+        <v>115.7123</v>
       </c>
       <c r="C57" s="15">
-        <v>-0.46</v>
+        <v>-0.25</v>
       </c>
       <c r="D57" s="16">
-        <v>2006960</v>
+        <v>2167476</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12"/>
@@ -1760,13 +1778,13 @@
         <v>63</v>
       </c>
       <c r="B58" s="14">
-        <v>118.0891</v>
+        <v>116.0035</v>
       </c>
       <c r="C58" s="15">
-        <v>-1.37</v>
+        <v>0.34</v>
       </c>
       <c r="D58" s="16">
-        <v>2000292</v>
+        <v>2169524</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12"/>
@@ -1776,13 +1794,13 @@
         <v>64</v>
       </c>
       <c r="B59" s="14">
-        <v>119.7273</v>
+        <v>115.6116</v>
       </c>
       <c r="C59" s="15">
-        <v>0.67</v>
+        <v>-0.76</v>
       </c>
       <c r="D59" s="16">
-        <v>1971192</v>
+        <v>2160109</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="12"/>
@@ -1792,13 +1810,13 @@
         <v>65</v>
       </c>
       <c r="B60" s="14">
-        <v>118.9325</v>
+        <v>116.4985</v>
       </c>
       <c r="C60" s="15">
-        <v>-0.5</v>
+        <v>-0.16</v>
       </c>
       <c r="D60" s="16">
-        <v>1893731</v>
+        <v>2089914</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12"/>
@@ -1808,13 +1826,13 @@
         <v>66</v>
       </c>
       <c r="B61" s="14">
-        <v>119.5293</v>
+        <v>116.6895</v>
       </c>
       <c r="C61" s="15">
-        <v>0.08</v>
+        <v>-0.4</v>
       </c>
       <c r="D61" s="16">
-        <v>1888886</v>
+        <v>2054650</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="12"/>
@@ -1824,13 +1842,13 @@
         <v>67</v>
       </c>
       <c r="B62" s="14">
-        <v>119.4377</v>
+        <v>117.1621</v>
       </c>
       <c r="C62" s="15">
-        <v>-0.04</v>
+        <v>-0.33</v>
       </c>
       <c r="D62" s="16">
-        <v>1875764</v>
+        <v>2020854</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="12"/>
@@ -1840,13 +1858,13 @@
         <v>68</v>
       </c>
       <c r="B63" s="14">
-        <v>119.4795</v>
+        <v>117.5474</v>
       </c>
       <c r="C63" s="15">
-        <v>0.45</v>
+        <v>-0.46</v>
       </c>
       <c r="D63" s="16">
-        <v>1882089</v>
+        <v>2006960</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="12"/>
@@ -1856,13 +1874,13 @@
         <v>69</v>
       </c>
       <c r="B64" s="14">
-        <v>118.9417</v>
+        <v>118.0891</v>
       </c>
       <c r="C64" s="15">
-        <v>0</v>
+        <v>-1.37</v>
       </c>
       <c r="D64" s="16">
-        <v>1874070</v>
+        <v>2000292</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12"/>
@@ -1872,13 +1890,13 @@
         <v>70</v>
       </c>
       <c r="B65" s="14">
-        <v>118.9381</v>
+        <v>119.7273</v>
       </c>
       <c r="C65" s="15">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="D65" s="16">
-        <v>1854936</v>
+        <v>1971192</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12"/>
@@ -1888,13 +1906,13 @@
         <v>71</v>
       </c>
       <c r="B66" s="14">
-        <v>118.5078</v>
+        <v>118.9325</v>
       </c>
       <c r="C66" s="15">
-        <v>0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="D66" s="16">
-        <v>1793350</v>
+        <v>1893731</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12"/>
@@ -1904,13 +1922,13 @@
         <v>72</v>
       </c>
       <c r="B67" s="14">
-        <v>118.0985</v>
+        <v>119.5293</v>
       </c>
       <c r="C67" s="15">
-        <v>0.49</v>
+        <v>0.08</v>
       </c>
       <c r="D67" s="16">
-        <v>1758312</v>
+        <v>1888886</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
@@ -1920,13 +1938,13 @@
         <v>73</v>
       </c>
       <c r="B68" s="14">
-        <v>117.5179</v>
+        <v>119.4377</v>
       </c>
       <c r="C68" s="15">
-        <v>0.56</v>
+        <v>-0.04</v>
       </c>
       <c r="D68" s="16">
-        <v>1738365</v>
+        <v>1875764</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12"/>
@@ -1936,13 +1954,13 @@
         <v>74</v>
       </c>
       <c r="B69" s="14">
-        <v>116.8645</v>
+        <v>119.4795</v>
       </c>
       <c r="C69" s="15">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="D69" s="16">
-        <v>1738745</v>
+        <v>1882089</v>
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="12"/>
@@ -1952,13 +1970,13 @@
         <v>75</v>
       </c>
       <c r="B70" s="14">
-        <v>116.4929</v>
+        <v>118.9417</v>
       </c>
       <c r="C70" s="15">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="D70" s="16">
-        <v>1751626</v>
+        <v>1874070</v>
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
@@ -1968,13 +1986,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="14">
-        <v>116.7245</v>
+        <v>118.9381</v>
       </c>
       <c r="C71" s="15">
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="D71" s="16">
-        <v>1751432</v>
+        <v>1854936</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
@@ -1984,13 +2002,13 @@
         <v>77</v>
       </c>
       <c r="B72" s="14">
-        <v>116.5503</v>
+        <v>118.5078</v>
       </c>
       <c r="C72" s="15">
-        <v>1.05</v>
+        <v>0.35</v>
       </c>
       <c r="D72" s="16">
-        <v>1698369</v>
+        <v>1793350</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
@@ -2000,13 +2018,13 @@
         <v>78</v>
       </c>
       <c r="B73" s="14">
-        <v>115.3388</v>
+        <v>118.0985</v>
       </c>
       <c r="C73" s="15">
-        <v>-0.29</v>
+        <v>0.49</v>
       </c>
       <c r="D73" s="16">
-        <v>1699227</v>
+        <v>1758312</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12"/>
@@ -2016,13 +2034,13 @@
         <v>79</v>
       </c>
       <c r="B74" s="14">
-        <v>115.6787</v>
+        <v>117.5179</v>
       </c>
       <c r="C74" s="15">
-        <v>-0.39</v>
+        <v>0.56</v>
       </c>
       <c r="D74" s="16">
-        <v>1700256</v>
+        <v>1738365</v>
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="12"/>
@@ -2032,13 +2050,13 @@
         <v>80</v>
       </c>
       <c r="B75" s="14">
-        <v>116.1297</v>
+        <v>116.8645</v>
       </c>
       <c r="C75" s="15">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="D75" s="16">
-        <v>1699127</v>
+        <v>1738745</v>
       </c>
       <c r="E75" s="12"/>
       <c r="F75" s="12"/>
@@ -2048,13 +2066,13 @@
         <v>81</v>
       </c>
       <c r="B76" s="14">
-        <v>115.7146</v>
+        <v>116.4929</v>
       </c>
       <c r="C76" s="15">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="D76" s="16">
-        <v>1686740</v>
+        <v>1751626</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="12"/>
@@ -2064,13 +2082,13 @@
         <v>82</v>
       </c>
       <c r="B77" s="14">
-        <v>115.733</v>
+        <v>116.7245</v>
       </c>
       <c r="C77" s="15">
-        <v>-0.01</v>
+        <v>0.15</v>
       </c>
       <c r="D77" s="16">
-        <v>1672215</v>
+        <v>1751432</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="12"/>
@@ -2080,13 +2098,13 @@
         <v>83</v>
       </c>
       <c r="B78" s="14">
-        <v>115.7457</v>
+        <v>116.5503</v>
       </c>
       <c r="C78" s="15">
-        <v>0.25</v>
+        <v>1.05</v>
       </c>
       <c r="D78" s="16">
-        <v>1631411</v>
+        <v>1698369</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="12"/>
@@ -2096,13 +2114,13 @@
         <v>84</v>
       </c>
       <c r="B79" s="14">
-        <v>115.4605</v>
+        <v>115.3388</v>
       </c>
       <c r="C79" s="15">
-        <v>0.12</v>
+        <v>-0.29</v>
       </c>
       <c r="D79" s="16">
-        <v>1612786</v>
+        <v>1699227</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="12"/>
@@ -2112,13 +2130,13 @@
         <v>85</v>
       </c>
       <c r="B80" s="14">
-        <v>115.3239</v>
+        <v>115.6787</v>
       </c>
       <c r="C80" s="15">
-        <v>-2.9</v>
+        <v>-0.39</v>
       </c>
       <c r="D80" s="16">
-        <v>1600185</v>
+        <v>1700256</v>
       </c>
       <c r="E80" s="12"/>
       <c r="F80" s="12"/>
@@ -2128,13 +2146,13 @@
         <v>86</v>
       </c>
       <c r="B81" s="14">
-        <v>118.7719</v>
+        <v>116.1297</v>
       </c>
       <c r="C81" s="15">
-        <v>-1.63</v>
+        <v>0.36</v>
       </c>
       <c r="D81" s="16">
-        <v>1591763</v>
+        <v>1699127</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12"/>
@@ -2144,13 +2162,13 @@
         <v>87</v>
       </c>
       <c r="B82" s="14">
-        <v>120.7441</v>
+        <v>115.7146</v>
       </c>
       <c r="C82" s="15">
-        <v>-0.66</v>
+        <v>-0.02</v>
       </c>
       <c r="D82" s="16">
-        <v>1567275</v>
+        <v>1686740</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="12"/>
@@ -2160,13 +2178,13 @@
         <v>88</v>
       </c>
       <c r="B83" s="14">
-        <v>121.5505</v>
+        <v>115.733</v>
       </c>
       <c r="C83" s="15">
-        <v>0.6</v>
+        <v>-0.01</v>
       </c>
       <c r="D83" s="16">
-        <v>1521574</v>
+        <v>1672215</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="12"/>
@@ -2176,13 +2194,13 @@
         <v>89</v>
       </c>
       <c r="B84" s="14">
-        <v>120.829</v>
+        <v>115.7457</v>
       </c>
       <c r="C84" s="15">
-        <v>0.63</v>
+        <v>0.25</v>
       </c>
       <c r="D84" s="16">
-        <v>1453341</v>
+        <v>1631411</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="12"/>
@@ -2192,13 +2210,13 @@
         <v>90</v>
       </c>
       <c r="B85" s="14">
-        <v>120.0786</v>
+        <v>115.4605</v>
       </c>
       <c r="C85" s="15">
-        <v>0.31</v>
+        <v>0.12</v>
       </c>
       <c r="D85" s="16">
-        <v>1434243</v>
+        <v>1612786</v>
       </c>
       <c r="E85" s="12"/>
       <c r="F85" s="12"/>
@@ -2208,13 +2226,13 @@
         <v>91</v>
       </c>
       <c r="B86" s="14">
-        <v>119.7137</v>
+        <v>115.3239</v>
       </c>
       <c r="C86" s="15">
-        <v>0.48</v>
+        <v>-2.9</v>
       </c>
       <c r="D86" s="16">
-        <v>1421467</v>
+        <v>1600185</v>
       </c>
       <c r="E86" s="12"/>
       <c r="F86" s="12"/>
@@ -2224,13 +2242,13 @@
         <v>92</v>
       </c>
       <c r="B87" s="14">
-        <v>119.1477</v>
+        <v>118.7719</v>
       </c>
       <c r="C87" s="15">
-        <v>-0.8</v>
+        <v>-1.63</v>
       </c>
       <c r="D87" s="16">
-        <v>1417271</v>
+        <v>1591763</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="12"/>
@@ -2240,13 +2258,13 @@
         <v>93</v>
       </c>
       <c r="B88" s="14">
-        <v>120.1108</v>
+        <v>120.7441</v>
       </c>
       <c r="C88" s="15">
-        <v>0.45</v>
+        <v>-0.66</v>
       </c>
       <c r="D88" s="16">
-        <v>1413776</v>
+        <v>1567275</v>
       </c>
       <c r="E88" s="12"/>
       <c r="F88" s="12"/>
@@ -2256,13 +2274,13 @@
         <v>94</v>
       </c>
       <c r="B89" s="14">
-        <v>119.5736</v>
+        <v>121.5505</v>
       </c>
       <c r="C89" s="15">
-        <v>1.16</v>
+        <v>0.6</v>
       </c>
       <c r="D89" s="16">
-        <v>1394330</v>
+        <v>1521574</v>
       </c>
       <c r="E89" s="12"/>
       <c r="F89" s="12"/>
@@ -2272,13 +2290,13 @@
         <v>95</v>
       </c>
       <c r="B90" s="14">
-        <v>118.2007</v>
+        <v>120.829</v>
       </c>
       <c r="C90" s="15">
-        <v>-1.28</v>
+        <v>0.63</v>
       </c>
       <c r="D90" s="16">
-        <v>1320181</v>
+        <v>1453341</v>
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="12"/>
@@ -2288,13 +2306,13 @@
         <v>96</v>
       </c>
       <c r="B91" s="14">
-        <v>119.7344</v>
+        <v>120.0786</v>
       </c>
       <c r="C91" s="15">
-        <v>0.94</v>
+        <v>0.31</v>
       </c>
       <c r="D91" s="16">
-        <v>1251436</v>
+        <v>1434243</v>
       </c>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
@@ -2304,13 +2322,13 @@
         <v>97</v>
       </c>
       <c r="B92" s="14">
-        <v>118.6189</v>
+        <v>119.7137</v>
       </c>
       <c r="C92" s="15">
-        <v>0.32</v>
+        <v>0.48</v>
       </c>
       <c r="D92" s="16">
-        <v>1198178</v>
+        <v>1421467</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="12"/>
@@ -2320,13 +2338,13 @@
         <v>98</v>
       </c>
       <c r="B93" s="14">
-        <v>118.2371</v>
+        <v>119.1477</v>
       </c>
       <c r="C93" s="15">
-        <v>0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="D93" s="16">
-        <v>1176051</v>
+        <v>1417271</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
@@ -2336,13 +2354,13 @@
         <v>99</v>
       </c>
       <c r="B94" s="14">
-        <v>117.5348</v>
+        <v>120.1108</v>
       </c>
       <c r="C94" s="15">
-        <v>0.81</v>
+        <v>0.45</v>
       </c>
       <c r="D94" s="16">
-        <v>1166186</v>
+        <v>1413776</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12"/>
@@ -2352,13 +2370,13 @@
         <v>100</v>
       </c>
       <c r="B95" s="14">
-        <v>116.5876</v>
+        <v>119.5736</v>
       </c>
       <c r="C95" s="15">
-        <v>-1.38</v>
+        <v>1.16</v>
       </c>
       <c r="D95" s="16">
-        <v>1138715</v>
+        <v>1394330</v>
       </c>
       <c r="E95" s="12"/>
       <c r="F95" s="12"/>
@@ -2368,13 +2386,13 @@
         <v>101</v>
       </c>
       <c r="B96" s="14">
-        <v>118.2224</v>
+        <v>118.2007</v>
       </c>
       <c r="C96" s="15">
-        <v>0.36</v>
+        <v>-1.28</v>
       </c>
       <c r="D96" s="16">
-        <v>1077702</v>
+        <v>1320181</v>
       </c>
       <c r="E96" s="12"/>
       <c r="F96" s="12"/>
@@ -2384,13 +2402,13 @@
         <v>102</v>
       </c>
       <c r="B97" s="14">
-        <v>117.8047</v>
+        <v>119.7344</v>
       </c>
       <c r="C97" s="15">
-        <v>-2.27</v>
+        <v>0.94</v>
       </c>
       <c r="D97" s="16">
-        <v>1057991</v>
+        <v>1251436</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="12"/>
@@ -2400,13 +2418,13 @@
         <v>103</v>
       </c>
       <c r="B98" s="14">
-        <v>120.5372</v>
+        <v>118.6189</v>
       </c>
       <c r="C98" s="15">
-        <v>0.11</v>
+        <v>0.32</v>
       </c>
       <c r="D98" s="16">
-        <v>1037402</v>
+        <v>1198178</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="12"/>
@@ -2416,13 +2434,13 @@
         <v>104</v>
       </c>
       <c r="B99" s="14">
-        <v>120.4034</v>
+        <v>118.2371</v>
       </c>
       <c r="C99" s="15">
-        <v>-0.29</v>
+        <v>0.6</v>
       </c>
       <c r="D99" s="16">
-        <v>1024926</v>
+        <v>1176051</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
@@ -2432,13 +2450,13 @@
         <v>105</v>
       </c>
       <c r="B100" s="14">
-        <v>120.7502</v>
+        <v>117.5348</v>
       </c>
       <c r="C100" s="15">
-        <v>0.73</v>
+        <v>0.81</v>
       </c>
       <c r="D100" s="16">
-        <v>1004562</v>
+        <v>1166186</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
@@ -2448,13 +2466,13 @@
         <v>106</v>
       </c>
       <c r="B101" s="14">
-        <v>119.8728</v>
+        <v>116.5876</v>
       </c>
       <c r="C101" s="15">
-        <v>-0.6</v>
+        <v>-1.38</v>
       </c>
       <c r="D101" s="16">
-        <v>970004</v>
+        <v>1138715</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="12"/>
@@ -2464,13 +2482,13 @@
         <v>107</v>
       </c>
       <c r="B102" s="14">
-        <v>120.6004</v>
+        <v>118.2224</v>
       </c>
       <c r="C102" s="15">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="D102" s="16">
-        <v>855569</v>
+        <v>1077702</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="12"/>
@@ -2480,13 +2498,13 @@
         <v>108</v>
       </c>
       <c r="B103" s="14">
-        <v>120.1746</v>
+        <v>117.8047</v>
       </c>
       <c r="C103" s="15">
-        <v>0.88</v>
+        <v>-2.27</v>
       </c>
       <c r="D103" s="16">
-        <v>812604</v>
+        <v>1057991</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
@@ -2496,13 +2514,13 @@
         <v>109</v>
       </c>
       <c r="B104" s="14">
-        <v>119.1224</v>
+        <v>120.5372</v>
       </c>
       <c r="C104" s="15">
-        <v>-0.61</v>
+        <v>0.11</v>
       </c>
       <c r="D104" s="16">
-        <v>779869</v>
+        <v>1037402</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="12"/>
@@ -2512,13 +2530,13 @@
         <v>110</v>
       </c>
       <c r="B105" s="14">
-        <v>119.8532</v>
+        <v>120.4034</v>
       </c>
       <c r="C105" s="15">
-        <v>-1.46</v>
+        <v>-0.29</v>
       </c>
       <c r="D105" s="16">
-        <v>707592</v>
+        <v>1024926</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="12"/>
@@ -2528,13 +2546,13 @@
         <v>111</v>
       </c>
       <c r="B106" s="14">
-        <v>121.6294</v>
+        <v>120.7502</v>
       </c>
       <c r="C106" s="15">
-        <v>1.12</v>
+        <v>0.73</v>
       </c>
       <c r="D106" s="16">
-        <v>674616</v>
+        <v>1004562</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="12"/>
@@ -2544,13 +2562,13 @@
         <v>112</v>
       </c>
       <c r="B107" s="14">
-        <v>120.2785</v>
+        <v>119.8728</v>
       </c>
       <c r="C107" s="15">
-        <v>-0.02</v>
+        <v>-0.6</v>
       </c>
       <c r="D107" s="16">
-        <v>638432</v>
+        <v>970004</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="12"/>
@@ -2560,13 +2578,13 @@
         <v>113</v>
       </c>
       <c r="B108" s="14">
-        <v>120.3006</v>
+        <v>120.6004</v>
       </c>
       <c r="C108" s="15">
-        <v>-0.33</v>
+        <v>0.35</v>
       </c>
       <c r="D108" s="16">
-        <v>582746</v>
+        <v>855569</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="12"/>
@@ -2576,13 +2594,13 @@
         <v>114</v>
       </c>
       <c r="B109" s="14">
-        <v>120.6971</v>
+        <v>120.1746</v>
       </c>
       <c r="C109" s="15">
-        <v>0.69</v>
+        <v>0.88</v>
       </c>
       <c r="D109" s="16">
-        <v>571304</v>
+        <v>812604</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="12"/>
@@ -2592,13 +2610,13 @@
         <v>115</v>
       </c>
       <c r="B110" s="14">
-        <v>119.8736</v>
+        <v>119.1224</v>
       </c>
       <c r="C110" s="15">
-        <v>1.12</v>
+        <v>-0.61</v>
       </c>
       <c r="D110" s="16">
-        <v>547899</v>
+        <v>779869</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="12"/>
@@ -2608,13 +2626,13 @@
         <v>116</v>
       </c>
       <c r="B111" s="14">
-        <v>118.5507</v>
+        <v>119.8532</v>
       </c>
       <c r="C111" s="15">
-        <v>-0.39</v>
+        <v>-1.46</v>
       </c>
       <c r="D111" s="16">
-        <v>539122</v>
+        <v>707592</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="12"/>
@@ -2624,13 +2642,13 @@
         <v>117</v>
       </c>
       <c r="B112" s="14">
-        <v>119.0084</v>
+        <v>121.6294</v>
       </c>
       <c r="C112" s="15">
-        <v>0.19</v>
+        <v>1.12</v>
       </c>
       <c r="D112" s="16">
-        <v>532531</v>
+        <v>674616</v>
       </c>
       <c r="E112" s="12"/>
       <c r="F112" s="12"/>
@@ -2640,13 +2658,13 @@
         <v>118</v>
       </c>
       <c r="B113" s="14">
-        <v>118.7797</v>
+        <v>120.2785</v>
       </c>
       <c r="C113" s="15">
-        <v>-0.64</v>
+        <v>-0.02</v>
       </c>
       <c r="D113" s="16">
-        <v>517833</v>
+        <v>638432</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="12"/>
@@ -2656,13 +2674,13 @@
         <v>119</v>
       </c>
       <c r="B114" s="14">
-        <v>119.5389</v>
+        <v>120.3006</v>
       </c>
       <c r="C114" s="15">
-        <v>0.48</v>
+        <v>-0.33</v>
       </c>
       <c r="D114" s="16">
-        <v>333809</v>
+        <v>582746</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="12"/>
@@ -2672,13 +2690,13 @@
         <v>120</v>
       </c>
       <c r="B115" s="14">
-        <v>118.9741</v>
+        <v>120.6971</v>
       </c>
       <c r="C115" s="15">
-        <v>0.47</v>
+        <v>0.69</v>
       </c>
       <c r="D115" s="16">
-        <v>303179</v>
+        <v>571304</v>
       </c>
       <c r="E115" s="12"/>
       <c r="F115" s="12"/>
@@ -2688,13 +2706,13 @@
         <v>121</v>
       </c>
       <c r="B116" s="14">
-        <v>118.4181</v>
+        <v>119.8736</v>
       </c>
       <c r="C116" s="15">
-        <v>0.74</v>
+        <v>1.12</v>
       </c>
       <c r="D116" s="16">
-        <v>279520</v>
+        <v>547899</v>
       </c>
       <c r="E116" s="12"/>
       <c r="F116" s="12"/>
@@ -2704,13 +2722,13 @@
         <v>122</v>
       </c>
       <c r="B117" s="14">
-        <v>117.5446</v>
+        <v>118.5507</v>
       </c>
       <c r="C117" s="15">
-        <v>0.11</v>
+        <v>-0.39</v>
       </c>
       <c r="D117" s="16">
-        <v>224344</v>
+        <v>539122</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="12"/>
@@ -2720,13 +2738,13 @@
         <v>123</v>
       </c>
       <c r="B118" s="14">
-        <v>117.4129</v>
+        <v>119.0084</v>
       </c>
       <c r="C118" s="15">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="D118" s="16">
-        <v>212999</v>
+        <v>532531</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="12"/>
@@ -2736,13 +2754,13 @@
         <v>124</v>
       </c>
       <c r="B119" s="14">
-        <v>117.2096</v>
+        <v>118.7797</v>
       </c>
       <c r="C119" s="15">
-        <v>1.02</v>
+        <v>-0.64</v>
       </c>
       <c r="D119" s="16">
-        <v>208472</v>
+        <v>517833</v>
       </c>
       <c r="E119" s="12"/>
       <c r="F119" s="12"/>
@@ -2752,13 +2770,13 @@
         <v>125</v>
       </c>
       <c r="B120" s="14">
-        <v>116.0317</v>
+        <v>119.5389</v>
       </c>
       <c r="C120" s="15">
-        <v>0.15</v>
+        <v>0.48</v>
       </c>
       <c r="D120" s="16">
-        <v>201455</v>
+        <v>333809</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="12"/>
@@ -2768,13 +2786,13 @@
         <v>126</v>
       </c>
       <c r="B121" s="14">
-        <v>115.8605</v>
+        <v>118.9741</v>
       </c>
       <c r="C121" s="15">
-        <v>0.17</v>
+        <v>0.47</v>
       </c>
       <c r="D121" s="16">
-        <v>177136</v>
+        <v>303179</v>
       </c>
       <c r="E121" s="12"/>
       <c r="F121" s="12"/>
@@ -2784,13 +2802,13 @@
         <v>127</v>
       </c>
       <c r="B122" s="14">
-        <v>115.6626</v>
+        <v>118.4181</v>
       </c>
       <c r="C122" s="15">
-        <v>-0.03</v>
+        <v>0.74</v>
       </c>
       <c r="D122" s="16">
-        <v>174672</v>
+        <v>279520</v>
       </c>
       <c r="E122" s="12"/>
       <c r="F122" s="12"/>
@@ -2800,13 +2818,13 @@
         <v>128</v>
       </c>
       <c r="B123" s="14">
-        <v>115.7003</v>
+        <v>117.5446</v>
       </c>
       <c r="C123" s="15">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="D123" s="16">
-        <v>174355</v>
+        <v>224344</v>
       </c>
       <c r="E123" s="12"/>
       <c r="F123" s="12"/>
@@ -2816,13 +2834,13 @@
         <v>129</v>
       </c>
       <c r="B124" s="14">
-        <v>115.6643</v>
+        <v>117.4129</v>
       </c>
       <c r="C124" s="15">
-        <v>1.26</v>
+        <v>0.17</v>
       </c>
       <c r="D124" s="16">
-        <v>171836</v>
+        <v>212999</v>
       </c>
       <c r="E124" s="12"/>
       <c r="F124" s="12"/>
@@ -2832,13 +2850,13 @@
         <v>130</v>
       </c>
       <c r="B125" s="14">
-        <v>114.2305</v>
+        <v>117.2096</v>
       </c>
       <c r="C125" s="15">
-        <v>-1.44</v>
+        <v>1.02</v>
       </c>
       <c r="D125" s="16">
-        <v>168640</v>
+        <v>208472</v>
       </c>
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
@@ -2848,13 +2866,13 @@
         <v>131</v>
       </c>
       <c r="B126" s="14">
-        <v>115.895</v>
+        <v>116.0317</v>
       </c>
       <c r="C126" s="15">
-        <v>0.52</v>
+        <v>0.15</v>
       </c>
       <c r="D126" s="16">
-        <v>152160</v>
+        <v>201455</v>
       </c>
       <c r="E126" s="12"/>
       <c r="F126" s="12"/>
@@ -2864,13 +2882,13 @@
         <v>132</v>
       </c>
       <c r="B127" s="14">
-        <v>115.2905</v>
+        <v>115.8605</v>
       </c>
       <c r="C127" s="15">
-        <v>0.29</v>
+        <v>0.17</v>
       </c>
       <c r="D127" s="16">
-        <v>139488</v>
+        <v>177136</v>
       </c>
       <c r="E127" s="12"/>
       <c r="F127" s="12"/>
@@ -2880,13 +2898,13 @@
         <v>133</v>
       </c>
       <c r="B128" s="14">
-        <v>114.9604</v>
+        <v>115.6626</v>
       </c>
       <c r="C128" s="15">
-        <v>0.42</v>
+        <v>-0.03</v>
       </c>
       <c r="D128" s="16">
-        <v>131512</v>
+        <v>174672</v>
       </c>
       <c r="E128" s="12"/>
       <c r="F128" s="12"/>
@@ -2896,13 +2914,13 @@
         <v>134</v>
       </c>
       <c r="B129" s="14">
-        <v>114.4793</v>
+        <v>115.7003</v>
       </c>
       <c r="C129" s="15">
-        <v>-0.69</v>
+        <v>0.03</v>
       </c>
       <c r="D129" s="16">
-        <v>98616</v>
+        <v>174355</v>
       </c>
       <c r="E129" s="12"/>
       <c r="F129" s="12"/>
@@ -2912,13 +2930,13 @@
         <v>135</v>
       </c>
       <c r="B130" s="14">
-        <v>115.2789</v>
+        <v>115.6643</v>
       </c>
       <c r="C130" s="15">
-        <v>-1.3</v>
+        <v>1.26</v>
       </c>
       <c r="D130" s="16">
-        <v>93368</v>
+        <v>171836</v>
       </c>
       <c r="E130" s="12"/>
       <c r="F130" s="12"/>
@@ -2928,13 +2946,13 @@
         <v>136</v>
       </c>
       <c r="B131" s="14">
-        <v>116.8004</v>
+        <v>114.2305</v>
       </c>
       <c r="C131" s="15">
-        <v>-1.03</v>
+        <v>-1.44</v>
       </c>
       <c r="D131" s="16">
-        <v>91265</v>
+        <v>168640</v>
       </c>
       <c r="E131" s="12"/>
       <c r="F131" s="12"/>
@@ -2944,13 +2962,13 @@
         <v>137</v>
       </c>
       <c r="B132" s="14">
-        <v>118.0124</v>
+        <v>115.895</v>
       </c>
       <c r="C132" s="15">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="D132" s="16">
-        <v>76329</v>
+        <v>152160</v>
       </c>
       <c r="E132" s="12"/>
       <c r="F132" s="12"/>
@@ -2960,13 +2978,13 @@
         <v>138</v>
       </c>
       <c r="B133" s="14">
-        <v>117.4107</v>
+        <v>115.2905</v>
       </c>
       <c r="C133" s="15">
-        <v>1.81</v>
+        <v>0.29</v>
       </c>
       <c r="D133" s="16">
-        <v>75528</v>
+        <v>139488</v>
       </c>
       <c r="E133" s="12"/>
       <c r="F133" s="12"/>
@@ -2976,13 +2994,13 @@
         <v>139</v>
       </c>
       <c r="B134" s="14">
-        <v>115.327</v>
+        <v>114.9604</v>
       </c>
       <c r="C134" s="15">
-        <v>-1.12</v>
+        <v>0.42</v>
       </c>
       <c r="D134" s="16">
-        <v>73900</v>
+        <v>131512</v>
       </c>
       <c r="E134" s="12"/>
       <c r="F134" s="12"/>
@@ -2992,13 +3010,13 @@
         <v>140</v>
       </c>
       <c r="B135" s="14">
-        <v>116.6346</v>
+        <v>114.4793</v>
       </c>
       <c r="C135" s="15">
-        <v>-2.13</v>
+        <v>-0.69</v>
       </c>
       <c r="D135" s="16">
-        <v>73925</v>
+        <v>98616</v>
       </c>
       <c r="E135" s="12"/>
       <c r="F135" s="12"/>
@@ -3008,13 +3026,13 @@
         <v>141</v>
       </c>
       <c r="B136" s="14">
-        <v>119.1731</v>
+        <v>115.2789</v>
       </c>
       <c r="C136" s="15">
-        <v>0.04</v>
+        <v>-1.3</v>
       </c>
       <c r="D136" s="16">
-        <v>71887</v>
+        <v>93368</v>
       </c>
       <c r="E136" s="12"/>
       <c r="F136" s="12"/>
@@ -3024,13 +3042,13 @@
         <v>142</v>
       </c>
       <c r="B137" s="14">
-        <v>119.124</v>
+        <v>116.8004</v>
       </c>
       <c r="C137" s="15">
-        <v>0.18</v>
+        <v>-1.03</v>
       </c>
       <c r="D137" s="16">
-        <v>67570</v>
+        <v>91265</v>
       </c>
       <c r="E137" s="12"/>
       <c r="F137" s="12"/>
@@ -3040,13 +3058,13 @@
         <v>143</v>
       </c>
       <c r="B138" s="14">
-        <v>118.9163</v>
+        <v>118.0124</v>
       </c>
       <c r="C138" s="15">
-        <v>-0.32</v>
+        <v>0.51</v>
       </c>
       <c r="D138" s="16">
-        <v>61350</v>
+        <v>76329</v>
       </c>
       <c r="E138" s="12"/>
       <c r="F138" s="12"/>
@@ -3056,13 +3074,13 @@
         <v>144</v>
       </c>
       <c r="B139" s="14">
-        <v>119.2963</v>
+        <v>117.4107</v>
       </c>
       <c r="C139" s="15">
-        <v>0.88</v>
+        <v>1.81</v>
       </c>
       <c r="D139" s="16">
-        <v>46208</v>
+        <v>75528</v>
       </c>
       <c r="E139" s="12"/>
       <c r="F139" s="12"/>
@@ -3072,13 +3090,13 @@
         <v>145</v>
       </c>
       <c r="B140" s="14">
-        <v>118.2555</v>
+        <v>115.327</v>
       </c>
       <c r="C140" s="15">
-        <v>0.43</v>
+        <v>-1.12</v>
       </c>
       <c r="D140" s="16">
-        <v>40390</v>
+        <v>73900</v>
       </c>
       <c r="E140" s="12"/>
       <c r="F140" s="12"/>
@@ -3088,13 +3106,13 @@
         <v>146</v>
       </c>
       <c r="B141" s="14">
-        <v>117.7545</v>
+        <v>116.6346</v>
       </c>
       <c r="C141" s="15">
-        <v>2.04</v>
+        <v>-2.13</v>
       </c>
       <c r="D141" s="16">
-        <v>39114</v>
+        <v>73925</v>
       </c>
       <c r="E141" s="12"/>
       <c r="F141" s="12"/>
@@ -3104,13 +3122,13 @@
         <v>147</v>
       </c>
       <c r="B142" s="14">
-        <v>115.4039</v>
+        <v>119.1731</v>
       </c>
       <c r="C142" s="15">
-        <v>1.17</v>
+        <v>0.04</v>
       </c>
       <c r="D142" s="16">
-        <v>38151</v>
+        <v>71887</v>
       </c>
       <c r="E142" s="12"/>
       <c r="F142" s="12"/>
@@ -3120,13 +3138,13 @@
         <v>148</v>
       </c>
       <c r="B143" s="14">
-        <v>114.0721</v>
+        <v>119.124</v>
       </c>
       <c r="C143" s="15">
-        <v>-0.42</v>
+        <v>0.18</v>
       </c>
       <c r="D143" s="16">
-        <v>37695</v>
+        <v>67570</v>
       </c>
       <c r="E143" s="12"/>
       <c r="F143" s="12"/>
@@ -3136,13 +3154,13 @@
         <v>149</v>
       </c>
       <c r="B144" s="14">
-        <v>114.5545</v>
+        <v>118.9163</v>
       </c>
       <c r="C144" s="15">
-        <v>1.15</v>
+        <v>-0.32</v>
       </c>
       <c r="D144" s="16">
-        <v>35320</v>
+        <v>61350</v>
       </c>
       <c r="E144" s="12"/>
       <c r="F144" s="12"/>
@@ -3152,13 +3170,13 @@
         <v>150</v>
       </c>
       <c r="B145" s="14">
-        <v>113.2502</v>
+        <v>119.2963</v>
       </c>
       <c r="C145" s="15">
-        <v>-0.7</v>
+        <v>0.88</v>
       </c>
       <c r="D145" s="16">
-        <v>33386</v>
+        <v>46208</v>
       </c>
       <c r="E145" s="12"/>
       <c r="F145" s="12"/>
@@ -3168,13 +3186,13 @@
         <v>151</v>
       </c>
       <c r="B146" s="14">
-        <v>114.0443</v>
+        <v>118.2555</v>
       </c>
       <c r="C146" s="15">
-        <v>0.23</v>
+        <v>0.43</v>
       </c>
       <c r="D146" s="16">
-        <v>29263</v>
+        <v>40390</v>
       </c>
       <c r="E146" s="12"/>
       <c r="F146" s="12"/>
@@ -3184,13 +3202,13 @@
         <v>152</v>
       </c>
       <c r="B147" s="14">
-        <v>113.7816</v>
+        <v>117.7545</v>
       </c>
       <c r="C147" s="15">
-        <v>-0.04</v>
+        <v>2.04</v>
       </c>
       <c r="D147" s="16">
-        <v>28746</v>
+        <v>39114</v>
       </c>
       <c r="E147" s="12"/>
       <c r="F147" s="12"/>
@@ -3200,13 +3218,13 @@
         <v>153</v>
       </c>
       <c r="B148" s="14">
-        <v>113.8293</v>
+        <v>115.4039</v>
       </c>
       <c r="C148" s="15">
-        <v>-0.2</v>
+        <v>1.17</v>
       </c>
       <c r="D148" s="16">
-        <v>27943</v>
+        <v>38151</v>
       </c>
       <c r="E148" s="12"/>
       <c r="F148" s="12"/>
@@ -3216,13 +3234,13 @@
         <v>154</v>
       </c>
       <c r="B149" s="14">
-        <v>114.0562</v>
+        <v>114.0721</v>
       </c>
       <c r="C149" s="15">
-        <v>-0.09</v>
+        <v>-0.42</v>
       </c>
       <c r="D149" s="16">
-        <v>25044</v>
+        <v>37695</v>
       </c>
       <c r="E149" s="12"/>
       <c r="F149" s="12"/>
@@ -3232,13 +3250,13 @@
         <v>155</v>
       </c>
       <c r="B150" s="14">
-        <v>114.162</v>
+        <v>114.5545</v>
       </c>
       <c r="C150" s="15">
-        <v>0.85</v>
+        <v>1.15</v>
       </c>
       <c r="D150" s="16">
-        <v>23532</v>
+        <v>35320</v>
       </c>
       <c r="E150" s="12"/>
       <c r="F150" s="12"/>
@@ -3248,13 +3266,13 @@
         <v>156</v>
       </c>
       <c r="B151" s="14">
-        <v>113.2012</v>
+        <v>113.2502</v>
       </c>
       <c r="C151" s="15">
-        <v>-0.02</v>
+        <v>-0.7</v>
       </c>
       <c r="D151" s="16">
-        <v>16418</v>
+        <v>33386</v>
       </c>
       <c r="E151" s="12"/>
       <c r="F151" s="12"/>
@@ -3264,13 +3282,13 @@
         <v>157</v>
       </c>
       <c r="B152" s="14">
-        <v>113.2186</v>
+        <v>114.0443</v>
       </c>
       <c r="C152" s="15">
-        <v>0.01</v>
+        <v>0.23</v>
       </c>
       <c r="D152" s="16">
-        <v>15405</v>
+        <v>29263</v>
       </c>
       <c r="E152" s="12"/>
       <c r="F152" s="12"/>
@@ -3280,13 +3298,13 @@
         <v>158</v>
       </c>
       <c r="B153" s="14">
-        <v>113.2047</v>
+        <v>113.7816</v>
       </c>
       <c r="C153" s="15">
-        <v>1.11</v>
+        <v>-0.04</v>
       </c>
       <c r="D153" s="16">
-        <v>14808</v>
+        <v>28746</v>
       </c>
       <c r="E153" s="12"/>
       <c r="F153" s="12"/>
@@ -3296,13 +3314,13 @@
         <v>159</v>
       </c>
       <c r="B154" s="14">
-        <v>111.9598</v>
+        <v>113.8293</v>
       </c>
       <c r="C154" s="15">
-        <v>-0.72</v>
+        <v>-0.2</v>
       </c>
       <c r="D154" s="16">
-        <v>13324</v>
+        <v>27943</v>
       </c>
       <c r="E154" s="12"/>
       <c r="F154" s="12"/>
@@ -3312,13 +3330,13 @@
         <v>160</v>
       </c>
       <c r="B155" s="14">
-        <v>112.7766</v>
+        <v>114.0562</v>
       </c>
       <c r="C155" s="15">
-        <v>0.38</v>
+        <v>-0.09</v>
       </c>
       <c r="D155" s="16">
-        <v>11951</v>
+        <v>25044</v>
       </c>
       <c r="E155" s="12"/>
       <c r="F155" s="12"/>
@@ -3328,13 +3346,13 @@
         <v>161</v>
       </c>
       <c r="B156" s="14">
-        <v>112.3461</v>
+        <v>114.162</v>
       </c>
       <c r="C156" s="15">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="D156" s="16">
-        <v>7638</v>
+        <v>23532</v>
       </c>
       <c r="E156" s="12"/>
       <c r="F156" s="12"/>
@@ -3344,13 +3362,13 @@
         <v>162</v>
       </c>
       <c r="B157" s="14">
-        <v>111.3676</v>
+        <v>113.2012</v>
       </c>
       <c r="C157" s="15">
-        <v>0.33</v>
+        <v>-0.02</v>
       </c>
       <c r="D157" s="16">
-        <v>6736</v>
+        <v>16418</v>
       </c>
       <c r="E157" s="12"/>
       <c r="F157" s="12"/>
@@ -3360,13 +3378,13 @@
         <v>163</v>
       </c>
       <c r="B158" s="14">
-        <v>111.0016</v>
+        <v>113.2186</v>
       </c>
       <c r="C158" s="15">
-        <v>1.47</v>
+        <v>0.01</v>
       </c>
       <c r="D158" s="16">
-        <v>6521</v>
+        <v>15405</v>
       </c>
       <c r="E158" s="12"/>
       <c r="F158" s="12"/>
@@ -3376,13 +3394,13 @@
         <v>164</v>
       </c>
       <c r="B159" s="14">
-        <v>109.3926</v>
+        <v>113.2047</v>
       </c>
       <c r="C159" s="15">
-        <v>-0.4</v>
+        <v>1.11</v>
       </c>
       <c r="D159" s="16">
-        <v>6147</v>
+        <v>14808</v>
       </c>
       <c r="E159" s="12"/>
       <c r="F159" s="12"/>
@@ -3392,13 +3410,13 @@
         <v>165</v>
       </c>
       <c r="B160" s="14">
-        <v>109.8347</v>
+        <v>111.9598</v>
       </c>
       <c r="C160" s="15">
-        <v>1.27</v>
+        <v>-0.72</v>
       </c>
       <c r="D160" s="16">
-        <v>5381</v>
+        <v>13324</v>
       </c>
       <c r="E160" s="12"/>
       <c r="F160" s="12"/>
@@ -3408,13 +3426,13 @@
         <v>166</v>
       </c>
       <c r="B161" s="14">
-        <v>108.4628</v>
+        <v>112.7766</v>
       </c>
       <c r="C161" s="15">
-        <v>-0.98</v>
+        <v>0.38</v>
       </c>
       <c r="D161" s="16">
-        <v>4975</v>
+        <v>11951</v>
       </c>
       <c r="E161" s="12"/>
       <c r="F161" s="12"/>
@@ -3424,13 +3442,13 @@
         <v>167</v>
       </c>
       <c r="B162" s="14">
-        <v>109.5329</v>
+        <v>112.3461</v>
       </c>
       <c r="C162" s="15">
-        <v>1.31</v>
+        <v>0.88</v>
       </c>
       <c r="D162" s="16">
-        <v>4423</v>
+        <v>7638</v>
       </c>
       <c r="E162" s="12"/>
       <c r="F162" s="12"/>
@@ -3440,13 +3458,13 @@
         <v>168</v>
       </c>
       <c r="B163" s="14">
-        <v>108.1217</v>
+        <v>111.3676</v>
       </c>
       <c r="C163" s="15">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="D163" s="16">
-        <v>1540</v>
+        <v>6736</v>
       </c>
       <c r="E163" s="12"/>
       <c r="F163" s="12"/>
@@ -3456,13 +3474,13 @@
         <v>169</v>
       </c>
       <c r="B164" s="14">
-        <v>107.2595</v>
+        <v>111.0016</v>
       </c>
       <c r="C164" s="15">
-        <v>0.68</v>
+        <v>1.47</v>
       </c>
       <c r="D164" s="16">
-        <v>1203</v>
+        <v>6521</v>
       </c>
       <c r="E164" s="12"/>
       <c r="F164" s="12"/>
@@ -3472,13 +3490,13 @@
         <v>170</v>
       </c>
       <c r="B165" s="14">
-        <v>106.5371</v>
+        <v>109.3926</v>
       </c>
       <c r="C165" s="15">
-        <v>-0.05</v>
+        <v>-0.4</v>
       </c>
       <c r="D165" s="16">
-        <v>1160</v>
+        <v>6147</v>
       </c>
       <c r="E165" s="12"/>
       <c r="F165" s="12"/>
@@ -3488,13 +3506,13 @@
         <v>171</v>
       </c>
       <c r="B166" s="14">
-        <v>106.5848</v>
+        <v>109.8347</v>
       </c>
       <c r="C166" s="15">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="D166" s="16">
-        <v>1087</v>
+        <v>5381</v>
       </c>
       <c r="E166" s="12"/>
       <c r="F166" s="12"/>
@@ -3504,13 +3522,13 @@
         <v>172</v>
       </c>
       <c r="B167" s="14">
-        <v>104.885</v>
+        <v>108.4628</v>
       </c>
       <c r="C167" s="15">
-        <v>0.88</v>
+        <v>-0.98</v>
       </c>
       <c r="D167" s="16">
-        <v>1064</v>
+        <v>4975</v>
       </c>
       <c r="E167" s="12"/>
       <c r="F167" s="12"/>
@@ -3520,13 +3538,13 @@
         <v>173</v>
       </c>
       <c r="B168" s="14">
-        <v>103.9697</v>
+        <v>109.5329</v>
       </c>
       <c r="C168" s="15">
-        <v>0.95</v>
+        <v>1.31</v>
       </c>
       <c r="D168" s="16">
-        <v>1007</v>
+        <v>4423</v>
       </c>
       <c r="E168" s="12"/>
       <c r="F168" s="12"/>
@@ -3536,13 +3554,13 @@
         <v>174</v>
       </c>
       <c r="B169" s="14">
-        <v>102.9955</v>
+        <v>108.1217</v>
       </c>
       <c r="C169" s="15">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="D169" s="16">
-        <v>1011</v>
+        <v>1540</v>
       </c>
       <c r="E169" s="12"/>
       <c r="F169" s="12"/>
@@ -3552,13 +3570,13 @@
         <v>175</v>
       </c>
       <c r="B170" s="14">
-        <v>102.8921</v>
+        <v>107.2595</v>
       </c>
       <c r="C170" s="15">
-        <v>0.3</v>
+        <v>0.68</v>
       </c>
       <c r="D170" s="16">
-        <v>1000</v>
+        <v>1203</v>
       </c>
       <c r="E170" s="12"/>
       <c r="F170" s="12"/>
@@ -3568,13 +3586,13 @@
         <v>176</v>
       </c>
       <c r="B171" s="14">
-        <v>102.5829</v>
+        <v>106.5371</v>
       </c>
       <c r="C171" s="15">
-        <v>0.75</v>
+        <v>-0.05</v>
       </c>
       <c r="D171" s="16">
-        <v>987</v>
+        <v>1160</v>
       </c>
       <c r="E171" s="12"/>
       <c r="F171" s="12"/>
@@ -3584,13 +3602,13 @@
         <v>177</v>
       </c>
       <c r="B172" s="14">
-        <v>101.8247</v>
+        <v>106.5848</v>
       </c>
       <c r="C172" s="15">
-        <v>0.37</v>
+        <v>1.62</v>
       </c>
       <c r="D172" s="16">
-        <v>823</v>
+        <v>1087</v>
       </c>
       <c r="E172" s="12"/>
       <c r="F172" s="12"/>
@@ -3600,13 +3618,13 @@
         <v>178</v>
       </c>
       <c r="B173" s="14">
-        <v>101.4515</v>
+        <v>104.885</v>
       </c>
       <c r="C173" s="15">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="D173" s="16">
-        <v>782</v>
+        <v>1064</v>
       </c>
       <c r="E173" s="12"/>
       <c r="F173" s="12"/>
@@ -3616,13 +3634,13 @@
         <v>179</v>
       </c>
       <c r="B174" s="14">
-        <v>100.5858</v>
+        <v>103.9697</v>
       </c>
       <c r="C174" s="15">
-        <v>-1.46</v>
+        <v>0.95</v>
       </c>
       <c r="D174" s="16">
-        <v>686</v>
+        <v>1007</v>
       </c>
       <c r="E174" s="12"/>
       <c r="F174" s="12"/>
@@ -3632,13 +3650,13 @@
         <v>180</v>
       </c>
       <c r="B175" s="14">
-        <v>102.0741</v>
+        <v>102.9955</v>
       </c>
       <c r="C175" s="15">
-        <v>-0.69</v>
+        <v>0.1</v>
       </c>
       <c r="D175" s="16">
-        <v>142</v>
+        <v>1011</v>
       </c>
       <c r="E175" s="12"/>
       <c r="F175" s="12"/>
@@ -3648,13 +3666,13 @@
         <v>181</v>
       </c>
       <c r="B176" s="14">
-        <v>102.7852</v>
+        <v>102.8921</v>
       </c>
       <c r="C176" s="15">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="D176" s="16">
-        <v>72</v>
+        <v>1000</v>
       </c>
       <c r="E176" s="12"/>
       <c r="F176" s="12"/>
@@ -3664,13 +3682,13 @@
         <v>182</v>
       </c>
       <c r="B177" s="14">
-        <v>102.4336</v>
+        <v>102.5829</v>
       </c>
       <c r="C177" s="15">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="D177" s="16">
-        <v>54</v>
+        <v>987</v>
       </c>
       <c r="E177" s="12"/>
       <c r="F177" s="12"/>
@@ -3680,13 +3698,13 @@
         <v>183</v>
       </c>
       <c r="B178" s="14">
-        <v>101.309</v>
+        <v>101.8247</v>
       </c>
       <c r="C178" s="15">
-        <v>1.31</v>
+        <v>0.37</v>
       </c>
       <c r="D178" s="16">
-        <v>53</v>
+        <v>823</v>
       </c>
       <c r="E178" s="12"/>
       <c r="F178" s="12"/>
@@ -3696,13 +3714,13 @@
         <v>184</v>
       </c>
       <c r="B179" s="14">
-        <v>100.0034</v>
+        <v>101.4515</v>
       </c>
       <c r="C179" s="15">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="D179" s="16">
-        <v>53</v>
+        <v>782</v>
       </c>
       <c r="E179" s="12"/>
       <c r="F179" s="12"/>
@@ -3712,29 +3730,125 @@
         <v>185</v>
       </c>
       <c r="B180" s="14">
-        <v>100</v>
-      </c>
-      <c r="C180" s="17" t="s">
-        <v>186</v>
+        <v>100.5858</v>
+      </c>
+      <c r="C180" s="15">
+        <v>-1.46</v>
       </c>
       <c r="D180" s="16">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="E180" s="12"/>
       <c r="F180" s="12"/>
     </row>
-    <row r="181" ht="35" customHeight="1">
-      <c r="A181" s="18" t="s">
+    <row r="181" s="12" customFormat="1">
+      <c r="A181" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B181" s="14">
+        <v>102.0741</v>
+      </c>
+      <c r="C181" s="15">
+        <v>-0.69</v>
+      </c>
+      <c r="D181" s="16">
+        <v>142</v>
+      </c>
+      <c r="E181" s="12"/>
+      <c r="F181" s="12"/>
+    </row>
+    <row r="182" s="12" customFormat="1">
+      <c r="A182" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="B181" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C181" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="D181" s="18" t="s">
-        <v>187</v>
+      <c r="B182" s="14">
+        <v>102.7852</v>
+      </c>
+      <c r="C182" s="15">
+        <v>0.34</v>
+      </c>
+      <c r="D182" s="16">
+        <v>72</v>
+      </c>
+      <c r="E182" s="12"/>
+      <c r="F182" s="12"/>
+    </row>
+    <row r="183" s="12" customFormat="1">
+      <c r="A183" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B183" s="14">
+        <v>102.4336</v>
+      </c>
+      <c r="C183" s="15">
+        <v>1.11</v>
+      </c>
+      <c r="D183" s="16">
+        <v>54</v>
+      </c>
+      <c r="E183" s="12"/>
+      <c r="F183" s="12"/>
+    </row>
+    <row r="184" s="12" customFormat="1">
+      <c r="A184" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B184" s="14">
+        <v>101.309</v>
+      </c>
+      <c r="C184" s="15">
+        <v>1.31</v>
+      </c>
+      <c r="D184" s="16">
+        <v>53</v>
+      </c>
+      <c r="E184" s="12"/>
+      <c r="F184" s="12"/>
+    </row>
+    <row r="185" s="12" customFormat="1">
+      <c r="A185" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B185" s="14">
+        <v>100.0034</v>
+      </c>
+      <c r="C185" s="15">
+        <v>0</v>
+      </c>
+      <c r="D185" s="16">
+        <v>53</v>
+      </c>
+      <c r="E185" s="12"/>
+      <c r="F185" s="12"/>
+    </row>
+    <row r="186" s="12" customFormat="1">
+      <c r="A186" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B186" s="14">
+        <v>100</v>
+      </c>
+      <c r="C186" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="D186" s="16">
+        <v>0</v>
+      </c>
+      <c r="E186" s="12"/>
+      <c r="F186" s="12"/>
+    </row>
+    <row r="187" ht="35" customHeight="1">
+      <c r="A187" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B187" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C187" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="D187" s="18" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3750,18 +3864,18 @@
     <mergeCell ref="E4:E4"/>
     <mergeCell ref="E5:E5"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A181:D181"/>
+    <mergeCell ref="A187:D187"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A6" location="'Historique Cours'!A181" display="Se rendre en bas du document"/>
-    <hyperlink ref="B6" location="'Historique Cours'!A181" display="Se rendre en bas du document"/>
-    <hyperlink ref="C6" location="'Historique Cours'!A181" display="Se rendre en bas du document"/>
-    <hyperlink ref="D6" location="'Historique Cours'!A181" display="Se rendre en bas du document"/>
-    <hyperlink ref="E6" location="'Historique Cours'!A181" display="Se rendre en bas du document"/>
-    <hyperlink ref="A181" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="B181" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="C181" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="D181" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="A6" location="'Historique Cours'!A187" display="Se rendre en bas du document"/>
+    <hyperlink ref="B6" location="'Historique Cours'!A187" display="Se rendre en bas du document"/>
+    <hyperlink ref="C6" location="'Historique Cours'!A187" display="Se rendre en bas du document"/>
+    <hyperlink ref="D6" location="'Historique Cours'!A187" display="Se rendre en bas du document"/>
+    <hyperlink ref="E6" location="'Historique Cours'!A187" display="Se rendre en bas du document"/>
+    <hyperlink ref="A187" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="B187" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="C187" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="D187" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
   </hyperlinks>
   <headerFooter/>
   <tableParts>
